--- a/docs/schedule/ガントチャート_v2.0.xlsx
+++ b/docs/schedule/ガントチャート_v2.0.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガント" sheetId="1" r:id="R33bd0daece574eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク一覧" sheetId="2" r:id="R6e4a677e2a7b4fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="3" r:id="R3d81ca6f956641a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガント" sheetId="1" r:id="R5c788b729ef74cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク一覧" sheetId="2" r:id="R5481c09bad3c4c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="3" r:id="Ra5afc34813194215"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -573,7 +573,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>田島組 卒業制作 ガントチャート v2.0（日別／基盤先行→feature分担）</x:v>
+        <x:v>田島組 卒業制作 ガントチャート v2.1（日別／基盤先行→最小MVPを8月末Web公開）</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -752,7 +752,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>作成日 2026-06-19 ／ 日付を 2026/06/01〜2026/11/15 まで1日ずつ表示 ／ 設定ボタン追加を完了タスクとして反映</x:v>
+        <x:v>更新 2026-06-26 ／ 主目標：2026/08/31 に最小機能アプリをWeb公開（M-MVP）／ 基盤完成 M-Base 7/15 ／ 拡張・中間発表は9〜11月</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -2219,26 +2219,26 @@
       <x:c r="FS7" s="9"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="9" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>p1b</x:v>
       </x:c>
-      <x:c r="B8" s="9" t="str">
-        <x:v>画面設計書（各画面）</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="str">
+      <x:c r="B8" s="10" t="str">
+        <x:v>画面設計書（ドラフト済）✅</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="str">
+      <x:c r="D8" s="10" t="str">
         <x:v>れん/ゆうと</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="str">
+      <x:c r="E8" s="10" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="str">
-        <x:v>7/1</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="str">
-        <x:v>7/20</x:v>
+      <x:c r="F8" s="10" t="str">
+        <x:v>6/24</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H8" s="9"/>
       <x:c r="I8" s="9"/>
@@ -2263,33 +2263,33 @@
       <x:c r="AB8" s="9"/>
       <x:c r="AC8" s="9"/>
       <x:c r="AD8" s="9"/>
-      <x:c r="AE8" s="9"/>
-      <x:c r="AF8" s="9"/>
-      <x:c r="AG8" s="9"/>
+      <x:c r="AE8" s="12"/>
+      <x:c r="AF8" s="12"/>
+      <x:c r="AG8" s="12"/>
       <x:c r="AH8" s="9"/>
       <x:c r="AI8" s="9"/>
       <x:c r="AJ8" s="9"/>
       <x:c r="AK8" s="9"/>
-      <x:c r="AL8" s="16"/>
-      <x:c r="AM8" s="16"/>
-      <x:c r="AN8" s="16"/>
-      <x:c r="AO8" s="16"/>
-      <x:c r="AP8" s="16"/>
-      <x:c r="AQ8" s="16"/>
-      <x:c r="AR8" s="16"/>
-      <x:c r="AS8" s="16"/>
-      <x:c r="AT8" s="16"/>
-      <x:c r="AU8" s="16"/>
-      <x:c r="AV8" s="16"/>
-      <x:c r="AW8" s="16"/>
-      <x:c r="AX8" s="16"/>
-      <x:c r="AY8" s="16"/>
-      <x:c r="AZ8" s="16"/>
-      <x:c r="BA8" s="16"/>
-      <x:c r="BB8" s="16"/>
-      <x:c r="BC8" s="16"/>
-      <x:c r="BD8" s="16"/>
-      <x:c r="BE8" s="16"/>
+      <x:c r="AL8" s="9"/>
+      <x:c r="AM8" s="9"/>
+      <x:c r="AN8" s="9"/>
+      <x:c r="AO8" s="9"/>
+      <x:c r="AP8" s="9"/>
+      <x:c r="AQ8" s="9"/>
+      <x:c r="AR8" s="9"/>
+      <x:c r="AS8" s="9"/>
+      <x:c r="AT8" s="9"/>
+      <x:c r="AU8" s="9"/>
+      <x:c r="AV8" s="9"/>
+      <x:c r="AW8" s="9"/>
+      <x:c r="AX8" s="9"/>
+      <x:c r="AY8" s="9"/>
+      <x:c r="AZ8" s="9"/>
+      <x:c r="BA8" s="9"/>
+      <x:c r="BB8" s="9"/>
+      <x:c r="BC8" s="9"/>
+      <x:c r="BD8" s="9"/>
+      <x:c r="BE8" s="9"/>
       <x:c r="BF8" s="9"/>
       <x:c r="BG8" s="9"/>
       <x:c r="BH8" s="9"/>
@@ -2410,26 +2410,26 @@
       <x:c r="FS8" s="9"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="9" t="str">
+      <x:c r="A9" s="10" t="str">
         <x:v>p1c</x:v>
       </x:c>
-      <x:c r="B9" s="9" t="str">
-        <x:v>DB設計書（ER・テーブル定義）</x:v>
-      </x:c>
-      <x:c r="C9" s="9" t="str">
+      <x:c r="B9" s="10" t="str">
+        <x:v>DB設計書（ドラフト済）✅</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="D9" s="9" t="str">
+      <x:c r="D9" s="10" t="str">
         <x:v>ひろと</x:v>
       </x:c>
-      <x:c r="E9" s="9" t="str">
+      <x:c r="E9" s="10" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="str">
-        <x:v>7/1</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="str">
-        <x:v>7/15</x:v>
+      <x:c r="F9" s="10" t="str">
+        <x:v>6/24</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H9" s="9"/>
       <x:c r="I9" s="9"/>
@@ -2454,28 +2454,28 @@
       <x:c r="AB9" s="9"/>
       <x:c r="AC9" s="9"/>
       <x:c r="AD9" s="9"/>
-      <x:c r="AE9" s="9"/>
-      <x:c r="AF9" s="9"/>
-      <x:c r="AG9" s="9"/>
+      <x:c r="AE9" s="12"/>
+      <x:c r="AF9" s="12"/>
+      <x:c r="AG9" s="12"/>
       <x:c r="AH9" s="9"/>
       <x:c r="AI9" s="9"/>
       <x:c r="AJ9" s="9"/>
       <x:c r="AK9" s="9"/>
-      <x:c r="AL9" s="16"/>
-      <x:c r="AM9" s="16"/>
-      <x:c r="AN9" s="16"/>
-      <x:c r="AO9" s="16"/>
-      <x:c r="AP9" s="16"/>
-      <x:c r="AQ9" s="16"/>
-      <x:c r="AR9" s="16"/>
-      <x:c r="AS9" s="16"/>
-      <x:c r="AT9" s="16"/>
-      <x:c r="AU9" s="16"/>
-      <x:c r="AV9" s="16"/>
-      <x:c r="AW9" s="16"/>
-      <x:c r="AX9" s="16"/>
-      <x:c r="AY9" s="16"/>
-      <x:c r="AZ9" s="16"/>
+      <x:c r="AL9" s="9"/>
+      <x:c r="AM9" s="9"/>
+      <x:c r="AN9" s="9"/>
+      <x:c r="AO9" s="9"/>
+      <x:c r="AP9" s="9"/>
+      <x:c r="AQ9" s="9"/>
+      <x:c r="AR9" s="9"/>
+      <x:c r="AS9" s="9"/>
+      <x:c r="AT9" s="9"/>
+      <x:c r="AU9" s="9"/>
+      <x:c r="AV9" s="9"/>
+      <x:c r="AW9" s="9"/>
+      <x:c r="AX9" s="9"/>
+      <x:c r="AY9" s="9"/>
+      <x:c r="AZ9" s="9"/>
       <x:c r="BA9" s="9"/>
       <x:c r="BB9" s="9"/>
       <x:c r="BC9" s="9"/>
@@ -2601,26 +2601,26 @@
       <x:c r="FS9" s="9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="9" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>p1d</x:v>
       </x:c>
-      <x:c r="B10" s="9" t="str">
-        <x:v>診断/推薦ロジック仕様</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="str">
+      <x:c r="B10" s="10" t="str">
+        <x:v>診断/推薦ロジック仕様（ドラフト済）✅</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="D10" s="9" t="str">
+      <x:c r="D10" s="10" t="str">
         <x:v>ひろと/たかと</x:v>
       </x:c>
-      <x:c r="E10" s="9" t="str">
+      <x:c r="E10" s="10" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="F10" s="9" t="str">
-        <x:v>7/8</x:v>
-      </x:c>
-      <x:c r="G10" s="9" t="str">
-        <x:v>7/25</x:v>
+      <x:c r="F10" s="10" t="str">
+        <x:v>6/24</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H10" s="9"/>
       <x:c r="I10" s="9"/>
@@ -2645,9 +2645,9 @@
       <x:c r="AB10" s="9"/>
       <x:c r="AC10" s="9"/>
       <x:c r="AD10" s="9"/>
-      <x:c r="AE10" s="9"/>
-      <x:c r="AF10" s="9"/>
-      <x:c r="AG10" s="9"/>
+      <x:c r="AE10" s="12"/>
+      <x:c r="AF10" s="12"/>
+      <x:c r="AG10" s="12"/>
       <x:c r="AH10" s="9"/>
       <x:c r="AI10" s="9"/>
       <x:c r="AJ10" s="9"/>
@@ -2659,24 +2659,24 @@
       <x:c r="AP10" s="9"/>
       <x:c r="AQ10" s="9"/>
       <x:c r="AR10" s="9"/>
-      <x:c r="AS10" s="16"/>
-      <x:c r="AT10" s="16"/>
-      <x:c r="AU10" s="16"/>
-      <x:c r="AV10" s="16"/>
-      <x:c r="AW10" s="16"/>
-      <x:c r="AX10" s="16"/>
-      <x:c r="AY10" s="16"/>
-      <x:c r="AZ10" s="16"/>
-      <x:c r="BA10" s="16"/>
-      <x:c r="BB10" s="16"/>
-      <x:c r="BC10" s="16"/>
-      <x:c r="BD10" s="16"/>
-      <x:c r="BE10" s="16"/>
-      <x:c r="BF10" s="16"/>
-      <x:c r="BG10" s="16"/>
-      <x:c r="BH10" s="16"/>
-      <x:c r="BI10" s="16"/>
-      <x:c r="BJ10" s="16"/>
+      <x:c r="AS10" s="9"/>
+      <x:c r="AT10" s="9"/>
+      <x:c r="AU10" s="9"/>
+      <x:c r="AV10" s="9"/>
+      <x:c r="AW10" s="9"/>
+      <x:c r="AX10" s="9"/>
+      <x:c r="AY10" s="9"/>
+      <x:c r="AZ10" s="9"/>
+      <x:c r="BA10" s="9"/>
+      <x:c r="BB10" s="9"/>
+      <x:c r="BC10" s="9"/>
+      <x:c r="BD10" s="9"/>
+      <x:c r="BE10" s="9"/>
+      <x:c r="BF10" s="9"/>
+      <x:c r="BG10" s="9"/>
+      <x:c r="BH10" s="9"/>
+      <x:c r="BI10" s="9"/>
+      <x:c r="BJ10" s="9"/>
       <x:c r="BK10" s="9"/>
       <x:c r="BL10" s="9"/>
       <x:c r="BM10" s="9"/>
@@ -2792,26 +2792,26 @@
       <x:c r="FS10" s="9"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="9" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>p1f</x:v>
       </x:c>
-      <x:c r="B11" s="9" t="str">
-        <x:v>薬機法準拠ガイドライン</x:v>
-      </x:c>
-      <x:c r="C11" s="9" t="str">
+      <x:c r="B11" s="10" t="str">
+        <x:v>薬機法準拠ガイドライン（ドラフト済）✅</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="D11" s="9" t="str">
+      <x:c r="D11" s="10" t="str">
         <x:v>たかと</x:v>
       </x:c>
-      <x:c r="E11" s="9" t="str">
+      <x:c r="E11" s="10" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="F11" s="9" t="str">
-        <x:v>7/1</x:v>
-      </x:c>
-      <x:c r="G11" s="9" t="str">
-        <x:v>7/18</x:v>
+      <x:c r="F11" s="10" t="str">
+        <x:v>6/24</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H11" s="9"/>
       <x:c r="I11" s="9"/>
@@ -2836,31 +2836,31 @@
       <x:c r="AB11" s="9"/>
       <x:c r="AC11" s="9"/>
       <x:c r="AD11" s="9"/>
-      <x:c r="AE11" s="9"/>
-      <x:c r="AF11" s="9"/>
-      <x:c r="AG11" s="9"/>
+      <x:c r="AE11" s="12"/>
+      <x:c r="AF11" s="12"/>
+      <x:c r="AG11" s="12"/>
       <x:c r="AH11" s="9"/>
       <x:c r="AI11" s="9"/>
       <x:c r="AJ11" s="9"/>
       <x:c r="AK11" s="9"/>
-      <x:c r="AL11" s="16"/>
-      <x:c r="AM11" s="16"/>
-      <x:c r="AN11" s="16"/>
-      <x:c r="AO11" s="16"/>
-      <x:c r="AP11" s="16"/>
-      <x:c r="AQ11" s="16"/>
-      <x:c r="AR11" s="16"/>
-      <x:c r="AS11" s="16"/>
-      <x:c r="AT11" s="16"/>
-      <x:c r="AU11" s="16"/>
-      <x:c r="AV11" s="16"/>
-      <x:c r="AW11" s="16"/>
-      <x:c r="AX11" s="16"/>
-      <x:c r="AY11" s="16"/>
-      <x:c r="AZ11" s="16"/>
-      <x:c r="BA11" s="16"/>
-      <x:c r="BB11" s="16"/>
-      <x:c r="BC11" s="16"/>
+      <x:c r="AL11" s="9"/>
+      <x:c r="AM11" s="9"/>
+      <x:c r="AN11" s="9"/>
+      <x:c r="AO11" s="9"/>
+      <x:c r="AP11" s="9"/>
+      <x:c r="AQ11" s="9"/>
+      <x:c r="AR11" s="9"/>
+      <x:c r="AS11" s="9"/>
+      <x:c r="AT11" s="9"/>
+      <x:c r="AU11" s="9"/>
+      <x:c r="AV11" s="9"/>
+      <x:c r="AW11" s="9"/>
+      <x:c r="AX11" s="9"/>
+      <x:c r="AY11" s="9"/>
+      <x:c r="AZ11" s="9"/>
+      <x:c r="BA11" s="9"/>
+      <x:c r="BB11" s="9"/>
+      <x:c r="BC11" s="9"/>
       <x:c r="BD11" s="9"/>
       <x:c r="BE11" s="9"/>
       <x:c r="BF11" s="9"/>
@@ -2999,10 +2999,10 @@
         <x:v>基盤</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
+        <x:v>7/1</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="str">
         <x:v>7/10</x:v>
-      </x:c>
-      <x:c r="G12" s="9" t="str">
-        <x:v>7/25</x:v>
       </x:c>
       <x:c r="H12" s="9"/>
       <x:c r="I12" s="9"/>
@@ -3034,31 +3034,31 @@
       <x:c r="AI12" s="9"/>
       <x:c r="AJ12" s="9"/>
       <x:c r="AK12" s="9"/>
-      <x:c r="AL12" s="9"/>
-      <x:c r="AM12" s="9"/>
-      <x:c r="AN12" s="9"/>
-      <x:c r="AO12" s="9"/>
-      <x:c r="AP12" s="9"/>
-      <x:c r="AQ12" s="9"/>
-      <x:c r="AR12" s="9"/>
-      <x:c r="AS12" s="9"/>
-      <x:c r="AT12" s="9"/>
+      <x:c r="AL12" s="16"/>
+      <x:c r="AM12" s="16"/>
+      <x:c r="AN12" s="16"/>
+      <x:c r="AO12" s="16"/>
+      <x:c r="AP12" s="16"/>
+      <x:c r="AQ12" s="16"/>
+      <x:c r="AR12" s="16"/>
+      <x:c r="AS12" s="16"/>
+      <x:c r="AT12" s="16"/>
       <x:c r="AU12" s="16"/>
-      <x:c r="AV12" s="16"/>
-      <x:c r="AW12" s="16"/>
-      <x:c r="AX12" s="16"/>
-      <x:c r="AY12" s="16"/>
-      <x:c r="AZ12" s="16"/>
-      <x:c r="BA12" s="16"/>
-      <x:c r="BB12" s="16"/>
-      <x:c r="BC12" s="16"/>
-      <x:c r="BD12" s="16"/>
-      <x:c r="BE12" s="16"/>
-      <x:c r="BF12" s="16"/>
-      <x:c r="BG12" s="16"/>
-      <x:c r="BH12" s="16"/>
-      <x:c r="BI12" s="16"/>
-      <x:c r="BJ12" s="16"/>
+      <x:c r="AV12" s="9"/>
+      <x:c r="AW12" s="9"/>
+      <x:c r="AX12" s="9"/>
+      <x:c r="AY12" s="9"/>
+      <x:c r="AZ12" s="9"/>
+      <x:c r="BA12" s="9"/>
+      <x:c r="BB12" s="9"/>
+      <x:c r="BC12" s="9"/>
+      <x:c r="BD12" s="9"/>
+      <x:c r="BE12" s="9"/>
+      <x:c r="BF12" s="9"/>
+      <x:c r="BG12" s="9"/>
+      <x:c r="BH12" s="9"/>
+      <x:c r="BI12" s="9"/>
+      <x:c r="BJ12" s="9"/>
       <x:c r="BK12" s="9"/>
       <x:c r="BL12" s="9"/>
       <x:c r="BM12" s="9"/>
@@ -3575,7 +3575,7 @@
         <x:v>6/26</x:v>
       </x:c>
       <x:c r="G15" s="18" t="str">
-        <x:v>7/15</x:v>
+        <x:v>7/6</x:v>
       </x:c>
       <x:c r="H15" s="9"/>
       <x:c r="I15" s="9"/>
@@ -3602,26 +3602,26 @@
       <x:c r="AD15" s="9"/>
       <x:c r="AE15" s="9"/>
       <x:c r="AF15" s="9"/>
-      <x:c r="AG15" s="16"/>
-      <x:c r="AH15" s="16"/>
-      <x:c r="AI15" s="16"/>
-      <x:c r="AJ15" s="16"/>
-      <x:c r="AK15" s="16"/>
-      <x:c r="AL15" s="16"/>
-      <x:c r="AM15" s="16"/>
-      <x:c r="AN15" s="16"/>
-      <x:c r="AO15" s="16"/>
-      <x:c r="AP15" s="16"/>
-      <x:c r="AQ15" s="16"/>
-      <x:c r="AR15" s="16"/>
-      <x:c r="AS15" s="16"/>
-      <x:c r="AT15" s="16"/>
-      <x:c r="AU15" s="16"/>
-      <x:c r="AV15" s="16"/>
-      <x:c r="AW15" s="16"/>
-      <x:c r="AX15" s="16"/>
-      <x:c r="AY15" s="16"/>
-      <x:c r="AZ15" s="16"/>
+      <x:c r="AG15" s="14"/>
+      <x:c r="AH15" s="14"/>
+      <x:c r="AI15" s="14"/>
+      <x:c r="AJ15" s="14"/>
+      <x:c r="AK15" s="14"/>
+      <x:c r="AL15" s="14"/>
+      <x:c r="AM15" s="14"/>
+      <x:c r="AN15" s="14"/>
+      <x:c r="AO15" s="14"/>
+      <x:c r="AP15" s="14"/>
+      <x:c r="AQ15" s="14"/>
+      <x:c r="AR15" s="9"/>
+      <x:c r="AS15" s="9"/>
+      <x:c r="AT15" s="9"/>
+      <x:c r="AU15" s="9"/>
+      <x:c r="AV15" s="9"/>
+      <x:c r="AW15" s="9"/>
+      <x:c r="AX15" s="9"/>
+      <x:c r="AY15" s="9"/>
+      <x:c r="AZ15" s="9"/>
       <x:c r="BA15" s="9"/>
       <x:c r="BB15" s="9"/>
       <x:c r="BC15" s="9"/>
@@ -3766,7 +3766,7 @@
         <x:v>7/1</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
-        <x:v>7/18</x:v>
+        <x:v>7/10</x:v>
       </x:c>
       <x:c r="H16" s="9"/>
       <x:c r="I16" s="9"/>
@@ -3808,14 +3808,14 @@
       <x:c r="AS16" s="16"/>
       <x:c r="AT16" s="16"/>
       <x:c r="AU16" s="16"/>
-      <x:c r="AV16" s="16"/>
-      <x:c r="AW16" s="16"/>
-      <x:c r="AX16" s="16"/>
-      <x:c r="AY16" s="16"/>
-      <x:c r="AZ16" s="16"/>
-      <x:c r="BA16" s="16"/>
-      <x:c r="BB16" s="16"/>
-      <x:c r="BC16" s="16"/>
+      <x:c r="AV16" s="9"/>
+      <x:c r="AW16" s="9"/>
+      <x:c r="AX16" s="9"/>
+      <x:c r="AY16" s="9"/>
+      <x:c r="AZ16" s="9"/>
+      <x:c r="BA16" s="9"/>
+      <x:c r="BB16" s="9"/>
+      <x:c r="BC16" s="9"/>
       <x:c r="BD16" s="9"/>
       <x:c r="BE16" s="9"/>
       <x:c r="BF16" s="9"/>
@@ -3939,16 +3939,16 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="18" t="str">
-        <x:v>p2b</x:v>
+        <x:v>p2e</x:v>
       </x:c>
       <x:c r="B17" s="18" t="str">
-        <x:v>Supabase初期構築・RLS</x:v>
+        <x:v>ダミーデータ・型定義・基盤完成→developマージ</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
         <x:v>P2</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>村上/ひろと</x:v>
+        <x:v>村上</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
         <x:v>基盤</x:v>
@@ -3957,7 +3957,7 @@
         <x:v>7/8</x:v>
       </x:c>
       <x:c r="G17" s="18" t="str">
-        <x:v>7/22</x:v>
+        <x:v>7/15</x:v>
       </x:c>
       <x:c r="H17" s="9"/>
       <x:c r="I17" s="9"/>
@@ -4004,13 +4004,13 @@
       <x:c r="AX17" s="16"/>
       <x:c r="AY17" s="16"/>
       <x:c r="AZ17" s="16"/>
-      <x:c r="BA17" s="16"/>
-      <x:c r="BB17" s="16"/>
-      <x:c r="BC17" s="16"/>
-      <x:c r="BD17" s="16"/>
-      <x:c r="BE17" s="16"/>
-      <x:c r="BF17" s="16"/>
-      <x:c r="BG17" s="16"/>
+      <x:c r="BA17" s="9"/>
+      <x:c r="BB17" s="9"/>
+      <x:c r="BC17" s="9"/>
+      <x:c r="BD17" s="9"/>
+      <x:c r="BE17" s="9"/>
+      <x:c r="BF17" s="9"/>
+      <x:c r="BG17" s="9"/>
       <x:c r="BH17" s="9"/>
       <x:c r="BI17" s="9"/>
       <x:c r="BJ17" s="9"/>
@@ -4129,26 +4129,26 @@
       <x:c r="FS17" s="9"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="18" t="str">
-        <x:v>p2e</x:v>
-      </x:c>
-      <x:c r="B18" s="18" t="str">
-        <x:v>ダミーデータ・型定義・基盤完成→developマージ</x:v>
-      </x:c>
-      <x:c r="C18" s="18" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="str">
+      <x:c r="A18" s="9" t="str">
+        <x:v>mbase</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="str">
+        <x:v>★ M-Base 基盤アプリ完成（developマージ）</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="str">
+        <x:v>M</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="str">
         <x:v>村上</x:v>
       </x:c>
-      <x:c r="E18" s="18" t="str">
+      <x:c r="E18" s="9" t="str">
         <x:v>基盤</x:v>
       </x:c>
-      <x:c r="F18" s="18" t="str">
+      <x:c r="F18" s="9" t="str">
         <x:v>7/15</x:v>
       </x:c>
-      <x:c r="G18" s="18" t="str">
-        <x:v>7/31</x:v>
+      <x:c r="G18" s="9" t="str">
+        <x:v>7/15</x:v>
       </x:c>
       <x:c r="H18" s="9"/>
       <x:c r="I18" s="9"/>
@@ -4194,23 +4194,25 @@
       <x:c r="AW18" s="9"/>
       <x:c r="AX18" s="9"/>
       <x:c r="AY18" s="9"/>
-      <x:c r="AZ18" s="16"/>
-      <x:c r="BA18" s="16"/>
-      <x:c r="BB18" s="16"/>
-      <x:c r="BC18" s="16"/>
-      <x:c r="BD18" s="16"/>
-      <x:c r="BE18" s="16"/>
-      <x:c r="BF18" s="16"/>
-      <x:c r="BG18" s="16"/>
-      <x:c r="BH18" s="16"/>
-      <x:c r="BI18" s="16"/>
-      <x:c r="BJ18" s="16"/>
-      <x:c r="BK18" s="16"/>
-      <x:c r="BL18" s="16"/>
-      <x:c r="BM18" s="16"/>
-      <x:c r="BN18" s="16"/>
-      <x:c r="BO18" s="16"/>
-      <x:c r="BP18" s="16"/>
+      <x:c r="AZ18" s="20" t="str">
+        <x:v>◆</x:v>
+      </x:c>
+      <x:c r="BA18" s="9"/>
+      <x:c r="BB18" s="9"/>
+      <x:c r="BC18" s="9"/>
+      <x:c r="BD18" s="9"/>
+      <x:c r="BE18" s="9"/>
+      <x:c r="BF18" s="9"/>
+      <x:c r="BG18" s="9"/>
+      <x:c r="BH18" s="9"/>
+      <x:c r="BI18" s="9"/>
+      <x:c r="BJ18" s="9"/>
+      <x:c r="BK18" s="9"/>
+      <x:c r="BL18" s="9"/>
+      <x:c r="BM18" s="9"/>
+      <x:c r="BN18" s="9"/>
+      <x:c r="BO18" s="9"/>
+      <x:c r="BP18" s="9"/>
       <x:c r="BQ18" s="9"/>
       <x:c r="BR18" s="9"/>
       <x:c r="BS18" s="9"/>
@@ -4324,7 +4326,7 @@
         <x:v>p3a</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>商品マスター30-50整備</x:v>
+        <x:v>商品マスター 最小整備(15-20)</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
         <x:v>P3</x:v>
@@ -4336,10 +4338,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>8/1</x:v>
+        <x:v>7/10</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
-        <x:v>8/31</x:v>
+        <x:v>8/5</x:v>
       </x:c>
       <x:c r="H19" s="9"/>
       <x:c r="I19" s="9"/>
@@ -4380,59 +4382,59 @@
       <x:c r="AR19" s="9"/>
       <x:c r="AS19" s="9"/>
       <x:c r="AT19" s="9"/>
-      <x:c r="AU19" s="9"/>
-      <x:c r="AV19" s="9"/>
-      <x:c r="AW19" s="9"/>
-      <x:c r="AX19" s="9"/>
-      <x:c r="AY19" s="9"/>
-      <x:c r="AZ19" s="9"/>
-      <x:c r="BA19" s="9"/>
-      <x:c r="BB19" s="9"/>
-      <x:c r="BC19" s="9"/>
-      <x:c r="BD19" s="9"/>
-      <x:c r="BE19" s="9"/>
-      <x:c r="BF19" s="9"/>
-      <x:c r="BG19" s="9"/>
-      <x:c r="BH19" s="9"/>
-      <x:c r="BI19" s="9"/>
-      <x:c r="BJ19" s="9"/>
-      <x:c r="BK19" s="9"/>
-      <x:c r="BL19" s="9"/>
-      <x:c r="BM19" s="9"/>
-      <x:c r="BN19" s="9"/>
-      <x:c r="BO19" s="9"/>
-      <x:c r="BP19" s="9"/>
+      <x:c r="AU19" s="16"/>
+      <x:c r="AV19" s="16"/>
+      <x:c r="AW19" s="16"/>
+      <x:c r="AX19" s="16"/>
+      <x:c r="AY19" s="16"/>
+      <x:c r="AZ19" s="16"/>
+      <x:c r="BA19" s="16"/>
+      <x:c r="BB19" s="16"/>
+      <x:c r="BC19" s="16"/>
+      <x:c r="BD19" s="16"/>
+      <x:c r="BE19" s="16"/>
+      <x:c r="BF19" s="16"/>
+      <x:c r="BG19" s="16"/>
+      <x:c r="BH19" s="16"/>
+      <x:c r="BI19" s="16"/>
+      <x:c r="BJ19" s="16"/>
+      <x:c r="BK19" s="16"/>
+      <x:c r="BL19" s="16"/>
+      <x:c r="BM19" s="16"/>
+      <x:c r="BN19" s="16"/>
+      <x:c r="BO19" s="16"/>
+      <x:c r="BP19" s="16"/>
       <x:c r="BQ19" s="16"/>
       <x:c r="BR19" s="16"/>
       <x:c r="BS19" s="16"/>
       <x:c r="BT19" s="16"/>
       <x:c r="BU19" s="16"/>
-      <x:c r="BV19" s="16"/>
-      <x:c r="BW19" s="16"/>
-      <x:c r="BX19" s="16"/>
-      <x:c r="BY19" s="16"/>
-      <x:c r="BZ19" s="16"/>
-      <x:c r="CA19" s="16"/>
-      <x:c r="CB19" s="16"/>
-      <x:c r="CC19" s="16"/>
-      <x:c r="CD19" s="16"/>
-      <x:c r="CE19" s="16"/>
-      <x:c r="CF19" s="16"/>
-      <x:c r="CG19" s="16"/>
-      <x:c r="CH19" s="16"/>
-      <x:c r="CI19" s="16"/>
-      <x:c r="CJ19" s="16"/>
-      <x:c r="CK19" s="16"/>
-      <x:c r="CL19" s="16"/>
-      <x:c r="CM19" s="16"/>
-      <x:c r="CN19" s="16"/>
-      <x:c r="CO19" s="16"/>
-      <x:c r="CP19" s="16"/>
-      <x:c r="CQ19" s="16"/>
-      <x:c r="CR19" s="16"/>
-      <x:c r="CS19" s="16"/>
-      <x:c r="CT19" s="16"/>
-      <x:c r="CU19" s="16"/>
+      <x:c r="BV19" s="9"/>
+      <x:c r="BW19" s="9"/>
+      <x:c r="BX19" s="9"/>
+      <x:c r="BY19" s="9"/>
+      <x:c r="BZ19" s="9"/>
+      <x:c r="CA19" s="9"/>
+      <x:c r="CB19" s="9"/>
+      <x:c r="CC19" s="9"/>
+      <x:c r="CD19" s="9"/>
+      <x:c r="CE19" s="9"/>
+      <x:c r="CF19" s="9"/>
+      <x:c r="CG19" s="9"/>
+      <x:c r="CH19" s="9"/>
+      <x:c r="CI19" s="9"/>
+      <x:c r="CJ19" s="9"/>
+      <x:c r="CK19" s="9"/>
+      <x:c r="CL19" s="9"/>
+      <x:c r="CM19" s="9"/>
+      <x:c r="CN19" s="9"/>
+      <x:c r="CO19" s="9"/>
+      <x:c r="CP19" s="9"/>
+      <x:c r="CQ19" s="9"/>
+      <x:c r="CR19" s="9"/>
+      <x:c r="CS19" s="9"/>
+      <x:c r="CT19" s="9"/>
+      <x:c r="CU19" s="9"/>
       <x:c r="CV19" s="9"/>
       <x:c r="CW19" s="9"/>
       <x:c r="CX19" s="9"/>
@@ -4512,25 +4514,25 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="9" t="str">
-        <x:v>p3b</x:v>
+        <x:v>p3c</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>成分タグ・事実情報整備</x:v>
+        <x:v>ロードマップ概念データ</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
         <x:v>P3</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>たかと</x:v>
+        <x:v>たかと/ひろと</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>8/15</x:v>
+        <x:v>7/12</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
-        <x:v>9/5</x:v>
+        <x:v>8/2</x:v>
       </x:c>
       <x:c r="H20" s="9"/>
       <x:c r="I20" s="9"/>
@@ -4573,28 +4575,28 @@
       <x:c r="AT20" s="9"/>
       <x:c r="AU20" s="9"/>
       <x:c r="AV20" s="9"/>
-      <x:c r="AW20" s="9"/>
-      <x:c r="AX20" s="9"/>
-      <x:c r="AY20" s="9"/>
-      <x:c r="AZ20" s="9"/>
-      <x:c r="BA20" s="9"/>
-      <x:c r="BB20" s="9"/>
-      <x:c r="BC20" s="9"/>
-      <x:c r="BD20" s="9"/>
-      <x:c r="BE20" s="9"/>
-      <x:c r="BF20" s="9"/>
-      <x:c r="BG20" s="9"/>
-      <x:c r="BH20" s="9"/>
-      <x:c r="BI20" s="9"/>
-      <x:c r="BJ20" s="9"/>
-      <x:c r="BK20" s="9"/>
-      <x:c r="BL20" s="9"/>
-      <x:c r="BM20" s="9"/>
-      <x:c r="BN20" s="9"/>
-      <x:c r="BO20" s="9"/>
-      <x:c r="BP20" s="9"/>
-      <x:c r="BQ20" s="9"/>
-      <x:c r="BR20" s="9"/>
+      <x:c r="AW20" s="16"/>
+      <x:c r="AX20" s="16"/>
+      <x:c r="AY20" s="16"/>
+      <x:c r="AZ20" s="16"/>
+      <x:c r="BA20" s="16"/>
+      <x:c r="BB20" s="16"/>
+      <x:c r="BC20" s="16"/>
+      <x:c r="BD20" s="16"/>
+      <x:c r="BE20" s="16"/>
+      <x:c r="BF20" s="16"/>
+      <x:c r="BG20" s="16"/>
+      <x:c r="BH20" s="16"/>
+      <x:c r="BI20" s="16"/>
+      <x:c r="BJ20" s="16"/>
+      <x:c r="BK20" s="16"/>
+      <x:c r="BL20" s="16"/>
+      <x:c r="BM20" s="16"/>
+      <x:c r="BN20" s="16"/>
+      <x:c r="BO20" s="16"/>
+      <x:c r="BP20" s="16"/>
+      <x:c r="BQ20" s="16"/>
+      <x:c r="BR20" s="16"/>
       <x:c r="BS20" s="9"/>
       <x:c r="BT20" s="9"/>
       <x:c r="BU20" s="9"/>
@@ -4607,28 +4609,28 @@
       <x:c r="CB20" s="9"/>
       <x:c r="CC20" s="9"/>
       <x:c r="CD20" s="9"/>
-      <x:c r="CE20" s="16"/>
-      <x:c r="CF20" s="16"/>
-      <x:c r="CG20" s="16"/>
-      <x:c r="CH20" s="16"/>
-      <x:c r="CI20" s="16"/>
-      <x:c r="CJ20" s="16"/>
-      <x:c r="CK20" s="16"/>
-      <x:c r="CL20" s="16"/>
-      <x:c r="CM20" s="16"/>
-      <x:c r="CN20" s="16"/>
-      <x:c r="CO20" s="16"/>
-      <x:c r="CP20" s="16"/>
-      <x:c r="CQ20" s="16"/>
-      <x:c r="CR20" s="16"/>
-      <x:c r="CS20" s="16"/>
-      <x:c r="CT20" s="16"/>
-      <x:c r="CU20" s="16"/>
-      <x:c r="CV20" s="16"/>
-      <x:c r="CW20" s="16"/>
-      <x:c r="CX20" s="16"/>
-      <x:c r="CY20" s="16"/>
-      <x:c r="CZ20" s="16"/>
+      <x:c r="CE20" s="9"/>
+      <x:c r="CF20" s="9"/>
+      <x:c r="CG20" s="9"/>
+      <x:c r="CH20" s="9"/>
+      <x:c r="CI20" s="9"/>
+      <x:c r="CJ20" s="9"/>
+      <x:c r="CK20" s="9"/>
+      <x:c r="CL20" s="9"/>
+      <x:c r="CM20" s="9"/>
+      <x:c r="CN20" s="9"/>
+      <x:c r="CO20" s="9"/>
+      <x:c r="CP20" s="9"/>
+      <x:c r="CQ20" s="9"/>
+      <x:c r="CR20" s="9"/>
+      <x:c r="CS20" s="9"/>
+      <x:c r="CT20" s="9"/>
+      <x:c r="CU20" s="9"/>
+      <x:c r="CV20" s="9"/>
+      <x:c r="CW20" s="9"/>
+      <x:c r="CX20" s="9"/>
+      <x:c r="CY20" s="9"/>
+      <x:c r="CZ20" s="9"/>
       <x:c r="DA20" s="9"/>
       <x:c r="DB20" s="9"/>
       <x:c r="DC20" s="9"/>
@@ -4703,25 +4705,25 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="9" t="str">
-        <x:v>p3c</x:v>
+        <x:v>p3b</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>ロードマップ概念データ</x:v>
+        <x:v>成分タグ・事実情報整備</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
         <x:v>P3</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>たかと/ひろと</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="F21" s="9" t="str">
-        <x:v>8/20</x:v>
+        <x:v>7/20</x:v>
       </x:c>
       <x:c r="G21" s="9" t="str">
-        <x:v>9/10</x:v>
+        <x:v>8/10</x:v>
       </x:c>
       <x:c r="H21" s="9"/>
       <x:c r="I21" s="9"/>
@@ -4772,28 +4774,28 @@
       <x:c r="BB21" s="9"/>
       <x:c r="BC21" s="9"/>
       <x:c r="BD21" s="9"/>
-      <x:c r="BE21" s="9"/>
-      <x:c r="BF21" s="9"/>
-      <x:c r="BG21" s="9"/>
-      <x:c r="BH21" s="9"/>
-      <x:c r="BI21" s="9"/>
-      <x:c r="BJ21" s="9"/>
-      <x:c r="BK21" s="9"/>
-      <x:c r="BL21" s="9"/>
-      <x:c r="BM21" s="9"/>
-      <x:c r="BN21" s="9"/>
-      <x:c r="BO21" s="9"/>
-      <x:c r="BP21" s="9"/>
-      <x:c r="BQ21" s="9"/>
-      <x:c r="BR21" s="9"/>
-      <x:c r="BS21" s="9"/>
-      <x:c r="BT21" s="9"/>
-      <x:c r="BU21" s="9"/>
-      <x:c r="BV21" s="9"/>
-      <x:c r="BW21" s="9"/>
-      <x:c r="BX21" s="9"/>
-      <x:c r="BY21" s="9"/>
-      <x:c r="BZ21" s="9"/>
+      <x:c r="BE21" s="16"/>
+      <x:c r="BF21" s="16"/>
+      <x:c r="BG21" s="16"/>
+      <x:c r="BH21" s="16"/>
+      <x:c r="BI21" s="16"/>
+      <x:c r="BJ21" s="16"/>
+      <x:c r="BK21" s="16"/>
+      <x:c r="BL21" s="16"/>
+      <x:c r="BM21" s="16"/>
+      <x:c r="BN21" s="16"/>
+      <x:c r="BO21" s="16"/>
+      <x:c r="BP21" s="16"/>
+      <x:c r="BQ21" s="16"/>
+      <x:c r="BR21" s="16"/>
+      <x:c r="BS21" s="16"/>
+      <x:c r="BT21" s="16"/>
+      <x:c r="BU21" s="16"/>
+      <x:c r="BV21" s="16"/>
+      <x:c r="BW21" s="16"/>
+      <x:c r="BX21" s="16"/>
+      <x:c r="BY21" s="16"/>
+      <x:c r="BZ21" s="16"/>
       <x:c r="CA21" s="9"/>
       <x:c r="CB21" s="9"/>
       <x:c r="CC21" s="9"/>
@@ -4803,28 +4805,28 @@
       <x:c r="CG21" s="9"/>
       <x:c r="CH21" s="9"/>
       <x:c r="CI21" s="9"/>
-      <x:c r="CJ21" s="16"/>
-      <x:c r="CK21" s="16"/>
-      <x:c r="CL21" s="16"/>
-      <x:c r="CM21" s="16"/>
-      <x:c r="CN21" s="16"/>
-      <x:c r="CO21" s="16"/>
-      <x:c r="CP21" s="16"/>
-      <x:c r="CQ21" s="16"/>
-      <x:c r="CR21" s="16"/>
-      <x:c r="CS21" s="16"/>
-      <x:c r="CT21" s="16"/>
-      <x:c r="CU21" s="16"/>
-      <x:c r="CV21" s="16"/>
-      <x:c r="CW21" s="16"/>
-      <x:c r="CX21" s="16"/>
-      <x:c r="CY21" s="16"/>
-      <x:c r="CZ21" s="16"/>
-      <x:c r="DA21" s="16"/>
-      <x:c r="DB21" s="16"/>
-      <x:c r="DC21" s="16"/>
-      <x:c r="DD21" s="16"/>
-      <x:c r="DE21" s="16"/>
+      <x:c r="CJ21" s="9"/>
+      <x:c r="CK21" s="9"/>
+      <x:c r="CL21" s="9"/>
+      <x:c r="CM21" s="9"/>
+      <x:c r="CN21" s="9"/>
+      <x:c r="CO21" s="9"/>
+      <x:c r="CP21" s="9"/>
+      <x:c r="CQ21" s="9"/>
+      <x:c r="CR21" s="9"/>
+      <x:c r="CS21" s="9"/>
+      <x:c r="CT21" s="9"/>
+      <x:c r="CU21" s="9"/>
+      <x:c r="CV21" s="9"/>
+      <x:c r="CW21" s="9"/>
+      <x:c r="CX21" s="9"/>
+      <x:c r="CY21" s="9"/>
+      <x:c r="CZ21" s="9"/>
+      <x:c r="DA21" s="9"/>
+      <x:c r="DB21" s="9"/>
+      <x:c r="DC21" s="9"/>
+      <x:c r="DD21" s="9"/>
+      <x:c r="DE21" s="9"/>
       <x:c r="DF21" s="9"/>
       <x:c r="DG21" s="9"/>
       <x:c r="DH21" s="9"/>
@@ -4909,10 +4911,10 @@
         <x:v>feature/diagnosis-logic</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
-        <x:v>8/1</x:v>
+        <x:v>7/16</x:v>
       </x:c>
       <x:c r="G22" s="9" t="str">
-        <x:v>8/31</x:v>
+        <x:v>8/5</x:v>
       </x:c>
       <x:c r="H22" s="9"/>
       <x:c r="I22" s="9"/>
@@ -4959,53 +4961,53 @@
       <x:c r="AX22" s="9"/>
       <x:c r="AY22" s="9"/>
       <x:c r="AZ22" s="9"/>
-      <x:c r="BA22" s="9"/>
-      <x:c r="BB22" s="9"/>
-      <x:c r="BC22" s="9"/>
-      <x:c r="BD22" s="9"/>
-      <x:c r="BE22" s="9"/>
-      <x:c r="BF22" s="9"/>
-      <x:c r="BG22" s="9"/>
-      <x:c r="BH22" s="9"/>
-      <x:c r="BI22" s="9"/>
-      <x:c r="BJ22" s="9"/>
-      <x:c r="BK22" s="9"/>
-      <x:c r="BL22" s="9"/>
-      <x:c r="BM22" s="9"/>
-      <x:c r="BN22" s="9"/>
-      <x:c r="BO22" s="9"/>
-      <x:c r="BP22" s="9"/>
+      <x:c r="BA22" s="16"/>
+      <x:c r="BB22" s="16"/>
+      <x:c r="BC22" s="16"/>
+      <x:c r="BD22" s="16"/>
+      <x:c r="BE22" s="16"/>
+      <x:c r="BF22" s="16"/>
+      <x:c r="BG22" s="16"/>
+      <x:c r="BH22" s="16"/>
+      <x:c r="BI22" s="16"/>
+      <x:c r="BJ22" s="16"/>
+      <x:c r="BK22" s="16"/>
+      <x:c r="BL22" s="16"/>
+      <x:c r="BM22" s="16"/>
+      <x:c r="BN22" s="16"/>
+      <x:c r="BO22" s="16"/>
+      <x:c r="BP22" s="16"/>
       <x:c r="BQ22" s="16"/>
       <x:c r="BR22" s="16"/>
       <x:c r="BS22" s="16"/>
       <x:c r="BT22" s="16"/>
       <x:c r="BU22" s="16"/>
-      <x:c r="BV22" s="16"/>
-      <x:c r="BW22" s="16"/>
-      <x:c r="BX22" s="16"/>
-      <x:c r="BY22" s="16"/>
-      <x:c r="BZ22" s="16"/>
-      <x:c r="CA22" s="16"/>
-      <x:c r="CB22" s="16"/>
-      <x:c r="CC22" s="16"/>
-      <x:c r="CD22" s="16"/>
-      <x:c r="CE22" s="16"/>
-      <x:c r="CF22" s="16"/>
-      <x:c r="CG22" s="16"/>
-      <x:c r="CH22" s="16"/>
-      <x:c r="CI22" s="16"/>
-      <x:c r="CJ22" s="16"/>
-      <x:c r="CK22" s="16"/>
-      <x:c r="CL22" s="16"/>
-      <x:c r="CM22" s="16"/>
-      <x:c r="CN22" s="16"/>
-      <x:c r="CO22" s="16"/>
-      <x:c r="CP22" s="16"/>
-      <x:c r="CQ22" s="16"/>
-      <x:c r="CR22" s="16"/>
-      <x:c r="CS22" s="16"/>
-      <x:c r="CT22" s="16"/>
-      <x:c r="CU22" s="16"/>
+      <x:c r="BV22" s="9"/>
+      <x:c r="BW22" s="9"/>
+      <x:c r="BX22" s="9"/>
+      <x:c r="BY22" s="9"/>
+      <x:c r="BZ22" s="9"/>
+      <x:c r="CA22" s="9"/>
+      <x:c r="CB22" s="9"/>
+      <x:c r="CC22" s="9"/>
+      <x:c r="CD22" s="9"/>
+      <x:c r="CE22" s="9"/>
+      <x:c r="CF22" s="9"/>
+      <x:c r="CG22" s="9"/>
+      <x:c r="CH22" s="9"/>
+      <x:c r="CI22" s="9"/>
+      <x:c r="CJ22" s="9"/>
+      <x:c r="CK22" s="9"/>
+      <x:c r="CL22" s="9"/>
+      <x:c r="CM22" s="9"/>
+      <x:c r="CN22" s="9"/>
+      <x:c r="CO22" s="9"/>
+      <x:c r="CP22" s="9"/>
+      <x:c r="CQ22" s="9"/>
+      <x:c r="CR22" s="9"/>
+      <x:c r="CS22" s="9"/>
+      <x:c r="CT22" s="9"/>
+      <x:c r="CU22" s="9"/>
       <x:c r="CV22" s="9"/>
       <x:c r="CW22" s="9"/>
       <x:c r="CX22" s="9"/>
@@ -5100,10 +5102,10 @@
         <x:v>feature/sc01-check-ui</x:v>
       </x:c>
       <x:c r="F23" s="9" t="str">
-        <x:v>8/1</x:v>
+        <x:v>7/16</x:v>
       </x:c>
       <x:c r="G23" s="9" t="str">
-        <x:v>8/31</x:v>
+        <x:v>8/8</x:v>
       </x:c>
       <x:c r="H23" s="9"/>
       <x:c r="I23" s="9"/>
@@ -5150,22 +5152,22 @@
       <x:c r="AX23" s="9"/>
       <x:c r="AY23" s="9"/>
       <x:c r="AZ23" s="9"/>
-      <x:c r="BA23" s="9"/>
-      <x:c r="BB23" s="9"/>
-      <x:c r="BC23" s="9"/>
-      <x:c r="BD23" s="9"/>
-      <x:c r="BE23" s="9"/>
-      <x:c r="BF23" s="9"/>
-      <x:c r="BG23" s="9"/>
-      <x:c r="BH23" s="9"/>
-      <x:c r="BI23" s="9"/>
-      <x:c r="BJ23" s="9"/>
-      <x:c r="BK23" s="9"/>
-      <x:c r="BL23" s="9"/>
-      <x:c r="BM23" s="9"/>
-      <x:c r="BN23" s="9"/>
-      <x:c r="BO23" s="9"/>
-      <x:c r="BP23" s="9"/>
+      <x:c r="BA23" s="16"/>
+      <x:c r="BB23" s="16"/>
+      <x:c r="BC23" s="16"/>
+      <x:c r="BD23" s="16"/>
+      <x:c r="BE23" s="16"/>
+      <x:c r="BF23" s="16"/>
+      <x:c r="BG23" s="16"/>
+      <x:c r="BH23" s="16"/>
+      <x:c r="BI23" s="16"/>
+      <x:c r="BJ23" s="16"/>
+      <x:c r="BK23" s="16"/>
+      <x:c r="BL23" s="16"/>
+      <x:c r="BM23" s="16"/>
+      <x:c r="BN23" s="16"/>
+      <x:c r="BO23" s="16"/>
+      <x:c r="BP23" s="16"/>
       <x:c r="BQ23" s="16"/>
       <x:c r="BR23" s="16"/>
       <x:c r="BS23" s="16"/>
@@ -5174,29 +5176,29 @@
       <x:c r="BV23" s="16"/>
       <x:c r="BW23" s="16"/>
       <x:c r="BX23" s="16"/>
-      <x:c r="BY23" s="16"/>
-      <x:c r="BZ23" s="16"/>
-      <x:c r="CA23" s="16"/>
-      <x:c r="CB23" s="16"/>
-      <x:c r="CC23" s="16"/>
-      <x:c r="CD23" s="16"/>
-      <x:c r="CE23" s="16"/>
-      <x:c r="CF23" s="16"/>
-      <x:c r="CG23" s="16"/>
-      <x:c r="CH23" s="16"/>
-      <x:c r="CI23" s="16"/>
-      <x:c r="CJ23" s="16"/>
-      <x:c r="CK23" s="16"/>
-      <x:c r="CL23" s="16"/>
-      <x:c r="CM23" s="16"/>
-      <x:c r="CN23" s="16"/>
-      <x:c r="CO23" s="16"/>
-      <x:c r="CP23" s="16"/>
-      <x:c r="CQ23" s="16"/>
-      <x:c r="CR23" s="16"/>
-      <x:c r="CS23" s="16"/>
-      <x:c r="CT23" s="16"/>
-      <x:c r="CU23" s="16"/>
+      <x:c r="BY23" s="9"/>
+      <x:c r="BZ23" s="9"/>
+      <x:c r="CA23" s="9"/>
+      <x:c r="CB23" s="9"/>
+      <x:c r="CC23" s="9"/>
+      <x:c r="CD23" s="9"/>
+      <x:c r="CE23" s="9"/>
+      <x:c r="CF23" s="9"/>
+      <x:c r="CG23" s="9"/>
+      <x:c r="CH23" s="9"/>
+      <x:c r="CI23" s="9"/>
+      <x:c r="CJ23" s="9"/>
+      <x:c r="CK23" s="9"/>
+      <x:c r="CL23" s="9"/>
+      <x:c r="CM23" s="9"/>
+      <x:c r="CN23" s="9"/>
+      <x:c r="CO23" s="9"/>
+      <x:c r="CP23" s="9"/>
+      <x:c r="CQ23" s="9"/>
+      <x:c r="CR23" s="9"/>
+      <x:c r="CS23" s="9"/>
+      <x:c r="CT23" s="9"/>
+      <x:c r="CU23" s="9"/>
       <x:c r="CV23" s="9"/>
       <x:c r="CW23" s="9"/>
       <x:c r="CX23" s="9"/>
@@ -5291,10 +5293,10 @@
         <x:v>feature/roadmap-logic</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
-        <x:v>8/20</x:v>
+        <x:v>7/28</x:v>
       </x:c>
       <x:c r="G24" s="9" t="str">
-        <x:v>9/15</x:v>
+        <x:v>8/12</x:v>
       </x:c>
       <x:c r="H24" s="9"/>
       <x:c r="I24" s="9"/>
@@ -5353,22 +5355,22 @@
       <x:c r="BJ24" s="9"/>
       <x:c r="BK24" s="9"/>
       <x:c r="BL24" s="9"/>
-      <x:c r="BM24" s="9"/>
-      <x:c r="BN24" s="9"/>
-      <x:c r="BO24" s="9"/>
-      <x:c r="BP24" s="9"/>
-      <x:c r="BQ24" s="9"/>
-      <x:c r="BR24" s="9"/>
-      <x:c r="BS24" s="9"/>
-      <x:c r="BT24" s="9"/>
-      <x:c r="BU24" s="9"/>
-      <x:c r="BV24" s="9"/>
-      <x:c r="BW24" s="9"/>
-      <x:c r="BX24" s="9"/>
-      <x:c r="BY24" s="9"/>
-      <x:c r="BZ24" s="9"/>
-      <x:c r="CA24" s="9"/>
-      <x:c r="CB24" s="9"/>
+      <x:c r="BM24" s="16"/>
+      <x:c r="BN24" s="16"/>
+      <x:c r="BO24" s="16"/>
+      <x:c r="BP24" s="16"/>
+      <x:c r="BQ24" s="16"/>
+      <x:c r="BR24" s="16"/>
+      <x:c r="BS24" s="16"/>
+      <x:c r="BT24" s="16"/>
+      <x:c r="BU24" s="16"/>
+      <x:c r="BV24" s="16"/>
+      <x:c r="BW24" s="16"/>
+      <x:c r="BX24" s="16"/>
+      <x:c r="BY24" s="16"/>
+      <x:c r="BZ24" s="16"/>
+      <x:c r="CA24" s="16"/>
+      <x:c r="CB24" s="16"/>
       <x:c r="CC24" s="9"/>
       <x:c r="CD24" s="9"/>
       <x:c r="CE24" s="9"/>
@@ -5376,33 +5378,33 @@
       <x:c r="CG24" s="9"/>
       <x:c r="CH24" s="9"/>
       <x:c r="CI24" s="9"/>
-      <x:c r="CJ24" s="16"/>
-      <x:c r="CK24" s="16"/>
-      <x:c r="CL24" s="16"/>
-      <x:c r="CM24" s="16"/>
-      <x:c r="CN24" s="16"/>
-      <x:c r="CO24" s="16"/>
-      <x:c r="CP24" s="16"/>
-      <x:c r="CQ24" s="16"/>
-      <x:c r="CR24" s="16"/>
-      <x:c r="CS24" s="16"/>
-      <x:c r="CT24" s="16"/>
-      <x:c r="CU24" s="16"/>
-      <x:c r="CV24" s="16"/>
-      <x:c r="CW24" s="16"/>
-      <x:c r="CX24" s="16"/>
-      <x:c r="CY24" s="16"/>
-      <x:c r="CZ24" s="16"/>
-      <x:c r="DA24" s="16"/>
-      <x:c r="DB24" s="16"/>
-      <x:c r="DC24" s="16"/>
-      <x:c r="DD24" s="16"/>
-      <x:c r="DE24" s="16"/>
-      <x:c r="DF24" s="16"/>
-      <x:c r="DG24" s="16"/>
-      <x:c r="DH24" s="16"/>
-      <x:c r="DI24" s="16"/>
-      <x:c r="DJ24" s="16"/>
+      <x:c r="CJ24" s="9"/>
+      <x:c r="CK24" s="9"/>
+      <x:c r="CL24" s="9"/>
+      <x:c r="CM24" s="9"/>
+      <x:c r="CN24" s="9"/>
+      <x:c r="CO24" s="9"/>
+      <x:c r="CP24" s="9"/>
+      <x:c r="CQ24" s="9"/>
+      <x:c r="CR24" s="9"/>
+      <x:c r="CS24" s="9"/>
+      <x:c r="CT24" s="9"/>
+      <x:c r="CU24" s="9"/>
+      <x:c r="CV24" s="9"/>
+      <x:c r="CW24" s="9"/>
+      <x:c r="CX24" s="9"/>
+      <x:c r="CY24" s="9"/>
+      <x:c r="CZ24" s="9"/>
+      <x:c r="DA24" s="9"/>
+      <x:c r="DB24" s="9"/>
+      <x:c r="DC24" s="9"/>
+      <x:c r="DD24" s="9"/>
+      <x:c r="DE24" s="9"/>
+      <x:c r="DF24" s="9"/>
+      <x:c r="DG24" s="9"/>
+      <x:c r="DH24" s="9"/>
+      <x:c r="DI24" s="9"/>
+      <x:c r="DJ24" s="9"/>
       <x:c r="DK24" s="9"/>
       <x:c r="DL24" s="9"/>
       <x:c r="DM24" s="9"/>
@@ -5467,25 +5469,25 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="9" t="str">
-        <x:v>p4c</x:v>
+        <x:v>p4f</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>SC-02 ロードマップUI</x:v>
+        <x:v>ディスクレーマー共通部品</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>れん</x:v>
+        <x:v>村上</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>feature/sc02-roadmap-ui</x:v>
+        <x:v>基盤/feature</x:v>
       </x:c>
       <x:c r="F25" s="9" t="str">
-        <x:v>9/1</x:v>
+        <x:v>7/28</x:v>
       </x:c>
       <x:c r="G25" s="9" t="str">
-        <x:v>9/25</x:v>
+        <x:v>8/8</x:v>
       </x:c>
       <x:c r="H25" s="9"/>
       <x:c r="I25" s="9"/>
@@ -5544,18 +5546,18 @@
       <x:c r="BJ25" s="9"/>
       <x:c r="BK25" s="9"/>
       <x:c r="BL25" s="9"/>
-      <x:c r="BM25" s="9"/>
-      <x:c r="BN25" s="9"/>
-      <x:c r="BO25" s="9"/>
-      <x:c r="BP25" s="9"/>
-      <x:c r="BQ25" s="9"/>
-      <x:c r="BR25" s="9"/>
-      <x:c r="BS25" s="9"/>
-      <x:c r="BT25" s="9"/>
-      <x:c r="BU25" s="9"/>
-      <x:c r="BV25" s="9"/>
-      <x:c r="BW25" s="9"/>
-      <x:c r="BX25" s="9"/>
+      <x:c r="BM25" s="16"/>
+      <x:c r="BN25" s="16"/>
+      <x:c r="BO25" s="16"/>
+      <x:c r="BP25" s="16"/>
+      <x:c r="BQ25" s="16"/>
+      <x:c r="BR25" s="16"/>
+      <x:c r="BS25" s="16"/>
+      <x:c r="BT25" s="16"/>
+      <x:c r="BU25" s="16"/>
+      <x:c r="BV25" s="16"/>
+      <x:c r="BW25" s="16"/>
+      <x:c r="BX25" s="16"/>
       <x:c r="BY25" s="9"/>
       <x:c r="BZ25" s="9"/>
       <x:c r="CA25" s="9"/>
@@ -5579,31 +5581,31 @@
       <x:c r="CS25" s="9"/>
       <x:c r="CT25" s="9"/>
       <x:c r="CU25" s="9"/>
-      <x:c r="CV25" s="16"/>
-      <x:c r="CW25" s="16"/>
-      <x:c r="CX25" s="16"/>
-      <x:c r="CY25" s="16"/>
-      <x:c r="CZ25" s="16"/>
-      <x:c r="DA25" s="16"/>
-      <x:c r="DB25" s="16"/>
-      <x:c r="DC25" s="16"/>
-      <x:c r="DD25" s="16"/>
-      <x:c r="DE25" s="16"/>
-      <x:c r="DF25" s="16"/>
-      <x:c r="DG25" s="16"/>
-      <x:c r="DH25" s="16"/>
-      <x:c r="DI25" s="16"/>
-      <x:c r="DJ25" s="16"/>
-      <x:c r="DK25" s="16"/>
-      <x:c r="DL25" s="16"/>
-      <x:c r="DM25" s="16"/>
-      <x:c r="DN25" s="16"/>
-      <x:c r="DO25" s="16"/>
-      <x:c r="DP25" s="16"/>
-      <x:c r="DQ25" s="16"/>
-      <x:c r="DR25" s="16"/>
-      <x:c r="DS25" s="16"/>
-      <x:c r="DT25" s="16"/>
+      <x:c r="CV25" s="9"/>
+      <x:c r="CW25" s="9"/>
+      <x:c r="CX25" s="9"/>
+      <x:c r="CY25" s="9"/>
+      <x:c r="CZ25" s="9"/>
+      <x:c r="DA25" s="9"/>
+      <x:c r="DB25" s="9"/>
+      <x:c r="DC25" s="9"/>
+      <x:c r="DD25" s="9"/>
+      <x:c r="DE25" s="9"/>
+      <x:c r="DF25" s="9"/>
+      <x:c r="DG25" s="9"/>
+      <x:c r="DH25" s="9"/>
+      <x:c r="DI25" s="9"/>
+      <x:c r="DJ25" s="9"/>
+      <x:c r="DK25" s="9"/>
+      <x:c r="DL25" s="9"/>
+      <x:c r="DM25" s="9"/>
+      <x:c r="DN25" s="9"/>
+      <x:c r="DO25" s="9"/>
+      <x:c r="DP25" s="9"/>
+      <x:c r="DQ25" s="9"/>
+      <x:c r="DR25" s="9"/>
+      <x:c r="DS25" s="9"/>
+      <x:c r="DT25" s="9"/>
       <x:c r="DU25" s="9"/>
       <x:c r="DV25" s="9"/>
       <x:c r="DW25" s="9"/>
@@ -5658,25 +5660,25 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="9" t="str">
-        <x:v>p4h</x:v>
+        <x:v>p4c</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>推薦ロジック（純粋関数）</x:v>
+        <x:v>SC-02 ロードマップUI</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>たかと</x:v>
+        <x:v>れん</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>feature/recommend-logic</x:v>
+        <x:v>feature/sc02-roadmap-ui</x:v>
       </x:c>
       <x:c r="F26" s="9" t="str">
-        <x:v>9/1</x:v>
+        <x:v>8/1</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
-        <x:v>9/25</x:v>
+        <x:v>8/18</x:v>
       </x:c>
       <x:c r="H26" s="9"/>
       <x:c r="I26" s="9"/>
@@ -5739,24 +5741,24 @@
       <x:c r="BN26" s="9"/>
       <x:c r="BO26" s="9"/>
       <x:c r="BP26" s="9"/>
-      <x:c r="BQ26" s="9"/>
-      <x:c r="BR26" s="9"/>
-      <x:c r="BS26" s="9"/>
-      <x:c r="BT26" s="9"/>
-      <x:c r="BU26" s="9"/>
-      <x:c r="BV26" s="9"/>
-      <x:c r="BW26" s="9"/>
-      <x:c r="BX26" s="9"/>
-      <x:c r="BY26" s="9"/>
-      <x:c r="BZ26" s="9"/>
-      <x:c r="CA26" s="9"/>
-      <x:c r="CB26" s="9"/>
-      <x:c r="CC26" s="9"/>
-      <x:c r="CD26" s="9"/>
-      <x:c r="CE26" s="9"/>
-      <x:c r="CF26" s="9"/>
-      <x:c r="CG26" s="9"/>
-      <x:c r="CH26" s="9"/>
+      <x:c r="BQ26" s="16"/>
+      <x:c r="BR26" s="16"/>
+      <x:c r="BS26" s="16"/>
+      <x:c r="BT26" s="16"/>
+      <x:c r="BU26" s="16"/>
+      <x:c r="BV26" s="16"/>
+      <x:c r="BW26" s="16"/>
+      <x:c r="BX26" s="16"/>
+      <x:c r="BY26" s="16"/>
+      <x:c r="BZ26" s="16"/>
+      <x:c r="CA26" s="16"/>
+      <x:c r="CB26" s="16"/>
+      <x:c r="CC26" s="16"/>
+      <x:c r="CD26" s="16"/>
+      <x:c r="CE26" s="16"/>
+      <x:c r="CF26" s="16"/>
+      <x:c r="CG26" s="16"/>
+      <x:c r="CH26" s="16"/>
       <x:c r="CI26" s="9"/>
       <x:c r="CJ26" s="9"/>
       <x:c r="CK26" s="9"/>
@@ -5770,31 +5772,31 @@
       <x:c r="CS26" s="9"/>
       <x:c r="CT26" s="9"/>
       <x:c r="CU26" s="9"/>
-      <x:c r="CV26" s="16"/>
-      <x:c r="CW26" s="16"/>
-      <x:c r="CX26" s="16"/>
-      <x:c r="CY26" s="16"/>
-      <x:c r="CZ26" s="16"/>
-      <x:c r="DA26" s="16"/>
-      <x:c r="DB26" s="16"/>
-      <x:c r="DC26" s="16"/>
-      <x:c r="DD26" s="16"/>
-      <x:c r="DE26" s="16"/>
-      <x:c r="DF26" s="16"/>
-      <x:c r="DG26" s="16"/>
-      <x:c r="DH26" s="16"/>
-      <x:c r="DI26" s="16"/>
-      <x:c r="DJ26" s="16"/>
-      <x:c r="DK26" s="16"/>
-      <x:c r="DL26" s="16"/>
-      <x:c r="DM26" s="16"/>
-      <x:c r="DN26" s="16"/>
-      <x:c r="DO26" s="16"/>
-      <x:c r="DP26" s="16"/>
-      <x:c r="DQ26" s="16"/>
-      <x:c r="DR26" s="16"/>
-      <x:c r="DS26" s="16"/>
-      <x:c r="DT26" s="16"/>
+      <x:c r="CV26" s="9"/>
+      <x:c r="CW26" s="9"/>
+      <x:c r="CX26" s="9"/>
+      <x:c r="CY26" s="9"/>
+      <x:c r="CZ26" s="9"/>
+      <x:c r="DA26" s="9"/>
+      <x:c r="DB26" s="9"/>
+      <x:c r="DC26" s="9"/>
+      <x:c r="DD26" s="9"/>
+      <x:c r="DE26" s="9"/>
+      <x:c r="DF26" s="9"/>
+      <x:c r="DG26" s="9"/>
+      <x:c r="DH26" s="9"/>
+      <x:c r="DI26" s="9"/>
+      <x:c r="DJ26" s="9"/>
+      <x:c r="DK26" s="9"/>
+      <x:c r="DL26" s="9"/>
+      <x:c r="DM26" s="9"/>
+      <x:c r="DN26" s="9"/>
+      <x:c r="DO26" s="9"/>
+      <x:c r="DP26" s="9"/>
+      <x:c r="DQ26" s="9"/>
+      <x:c r="DR26" s="9"/>
+      <x:c r="DS26" s="9"/>
+      <x:c r="DT26" s="9"/>
       <x:c r="DU26" s="9"/>
       <x:c r="DV26" s="9"/>
       <x:c r="DW26" s="9"/>
@@ -5849,25 +5851,25 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="9" t="str">
-        <x:v>p4d</x:v>
+        <x:v>p4h</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>SC-03 商品比較UI</x:v>
+        <x:v>推薦ロジック（最小・純粋関数）</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>ゆうと</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>feature/sc03-product-compare-ui</x:v>
+        <x:v>feature/recommend-logic</x:v>
       </x:c>
       <x:c r="F27" s="9" t="str">
-        <x:v>9/15</x:v>
+        <x:v>8/1</x:v>
       </x:c>
       <x:c r="G27" s="9" t="str">
-        <x:v>10/10</x:v>
+        <x:v>8/15</x:v>
       </x:c>
       <x:c r="H27" s="9"/>
       <x:c r="I27" s="9"/>
@@ -5930,21 +5932,21 @@
       <x:c r="BN27" s="9"/>
       <x:c r="BO27" s="9"/>
       <x:c r="BP27" s="9"/>
-      <x:c r="BQ27" s="9"/>
-      <x:c r="BR27" s="9"/>
-      <x:c r="BS27" s="9"/>
-      <x:c r="BT27" s="9"/>
-      <x:c r="BU27" s="9"/>
-      <x:c r="BV27" s="9"/>
-      <x:c r="BW27" s="9"/>
-      <x:c r="BX27" s="9"/>
-      <x:c r="BY27" s="9"/>
-      <x:c r="BZ27" s="9"/>
-      <x:c r="CA27" s="9"/>
-      <x:c r="CB27" s="9"/>
-      <x:c r="CC27" s="9"/>
-      <x:c r="CD27" s="9"/>
-      <x:c r="CE27" s="9"/>
+      <x:c r="BQ27" s="16"/>
+      <x:c r="BR27" s="16"/>
+      <x:c r="BS27" s="16"/>
+      <x:c r="BT27" s="16"/>
+      <x:c r="BU27" s="16"/>
+      <x:c r="BV27" s="16"/>
+      <x:c r="BW27" s="16"/>
+      <x:c r="BX27" s="16"/>
+      <x:c r="BY27" s="16"/>
+      <x:c r="BZ27" s="16"/>
+      <x:c r="CA27" s="16"/>
+      <x:c r="CB27" s="16"/>
+      <x:c r="CC27" s="16"/>
+      <x:c r="CD27" s="16"/>
+      <x:c r="CE27" s="16"/>
       <x:c r="CF27" s="9"/>
       <x:c r="CG27" s="9"/>
       <x:c r="CH27" s="9"/>
@@ -5975,32 +5977,32 @@
       <x:c r="DG27" s="9"/>
       <x:c r="DH27" s="9"/>
       <x:c r="DI27" s="9"/>
-      <x:c r="DJ27" s="16"/>
-      <x:c r="DK27" s="16"/>
-      <x:c r="DL27" s="16"/>
-      <x:c r="DM27" s="16"/>
-      <x:c r="DN27" s="16"/>
-      <x:c r="DO27" s="16"/>
-      <x:c r="DP27" s="16"/>
-      <x:c r="DQ27" s="16"/>
-      <x:c r="DR27" s="16"/>
-      <x:c r="DS27" s="16"/>
-      <x:c r="DT27" s="16"/>
-      <x:c r="DU27" s="16"/>
-      <x:c r="DV27" s="16"/>
-      <x:c r="DW27" s="16"/>
-      <x:c r="DX27" s="16"/>
-      <x:c r="DY27" s="16"/>
-      <x:c r="DZ27" s="16"/>
-      <x:c r="EA27" s="16"/>
-      <x:c r="EB27" s="16"/>
-      <x:c r="EC27" s="16"/>
-      <x:c r="ED27" s="16"/>
-      <x:c r="EE27" s="16"/>
-      <x:c r="EF27" s="16"/>
-      <x:c r="EG27" s="16"/>
-      <x:c r="EH27" s="16"/>
-      <x:c r="EI27" s="16"/>
+      <x:c r="DJ27" s="9"/>
+      <x:c r="DK27" s="9"/>
+      <x:c r="DL27" s="9"/>
+      <x:c r="DM27" s="9"/>
+      <x:c r="DN27" s="9"/>
+      <x:c r="DO27" s="9"/>
+      <x:c r="DP27" s="9"/>
+      <x:c r="DQ27" s="9"/>
+      <x:c r="DR27" s="9"/>
+      <x:c r="DS27" s="9"/>
+      <x:c r="DT27" s="9"/>
+      <x:c r="DU27" s="9"/>
+      <x:c r="DV27" s="9"/>
+      <x:c r="DW27" s="9"/>
+      <x:c r="DX27" s="9"/>
+      <x:c r="DY27" s="9"/>
+      <x:c r="DZ27" s="9"/>
+      <x:c r="EA27" s="9"/>
+      <x:c r="EB27" s="9"/>
+      <x:c r="EC27" s="9"/>
+      <x:c r="ED27" s="9"/>
+      <x:c r="EE27" s="9"/>
+      <x:c r="EF27" s="9"/>
+      <x:c r="EG27" s="9"/>
+      <x:c r="EH27" s="9"/>
+      <x:c r="EI27" s="9"/>
       <x:c r="EJ27" s="9"/>
       <x:c r="EK27" s="9"/>
       <x:c r="EL27" s="9"/>
@@ -6040,10 +6042,10 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="9" t="str">
-        <x:v>p4e</x:v>
+        <x:v>p4d</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>SC-04 継続記録UI</x:v>
+        <x:v>SC-03 商品比較UI</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
         <x:v>P4</x:v>
@@ -6052,13 +6054,13 @@
         <x:v>ゆうと</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>feature/sc04-record-ui</x:v>
+        <x:v>feature/sc03-product-compare-ui</x:v>
       </x:c>
       <x:c r="F28" s="9" t="str">
-        <x:v>10/1</x:v>
+        <x:v>8/8</x:v>
       </x:c>
       <x:c r="G28" s="9" t="str">
-        <x:v>10/15</x:v>
+        <x:v>8/22</x:v>
       </x:c>
       <x:c r="H28" s="9"/>
       <x:c r="I28" s="9"/>
@@ -6128,21 +6130,21 @@
       <x:c r="BU28" s="9"/>
       <x:c r="BV28" s="9"/>
       <x:c r="BW28" s="9"/>
-      <x:c r="BX28" s="9"/>
-      <x:c r="BY28" s="9"/>
-      <x:c r="BZ28" s="9"/>
-      <x:c r="CA28" s="9"/>
-      <x:c r="CB28" s="9"/>
-      <x:c r="CC28" s="9"/>
-      <x:c r="CD28" s="9"/>
-      <x:c r="CE28" s="9"/>
-      <x:c r="CF28" s="9"/>
-      <x:c r="CG28" s="9"/>
-      <x:c r="CH28" s="9"/>
-      <x:c r="CI28" s="9"/>
-      <x:c r="CJ28" s="9"/>
-      <x:c r="CK28" s="9"/>
-      <x:c r="CL28" s="9"/>
+      <x:c r="BX28" s="16"/>
+      <x:c r="BY28" s="16"/>
+      <x:c r="BZ28" s="16"/>
+      <x:c r="CA28" s="16"/>
+      <x:c r="CB28" s="16"/>
+      <x:c r="CC28" s="16"/>
+      <x:c r="CD28" s="16"/>
+      <x:c r="CE28" s="16"/>
+      <x:c r="CF28" s="16"/>
+      <x:c r="CG28" s="16"/>
+      <x:c r="CH28" s="16"/>
+      <x:c r="CI28" s="16"/>
+      <x:c r="CJ28" s="16"/>
+      <x:c r="CK28" s="16"/>
+      <x:c r="CL28" s="16"/>
       <x:c r="CM28" s="9"/>
       <x:c r="CN28" s="9"/>
       <x:c r="CO28" s="9"/>
@@ -6182,21 +6184,21 @@
       <x:c r="DW28" s="9"/>
       <x:c r="DX28" s="9"/>
       <x:c r="DY28" s="9"/>
-      <x:c r="DZ28" s="16"/>
-      <x:c r="EA28" s="16"/>
-      <x:c r="EB28" s="16"/>
-      <x:c r="EC28" s="16"/>
-      <x:c r="ED28" s="16"/>
-      <x:c r="EE28" s="16"/>
-      <x:c r="EF28" s="16"/>
-      <x:c r="EG28" s="16"/>
-      <x:c r="EH28" s="16"/>
-      <x:c r="EI28" s="16"/>
-      <x:c r="EJ28" s="16"/>
-      <x:c r="EK28" s="16"/>
-      <x:c r="EL28" s="16"/>
-      <x:c r="EM28" s="16"/>
-      <x:c r="EN28" s="16"/>
+      <x:c r="DZ28" s="9"/>
+      <x:c r="EA28" s="9"/>
+      <x:c r="EB28" s="9"/>
+      <x:c r="EC28" s="9"/>
+      <x:c r="ED28" s="9"/>
+      <x:c r="EE28" s="9"/>
+      <x:c r="EF28" s="9"/>
+      <x:c r="EG28" s="9"/>
+      <x:c r="EH28" s="9"/>
+      <x:c r="EI28" s="9"/>
+      <x:c r="EJ28" s="9"/>
+      <x:c r="EK28" s="9"/>
+      <x:c r="EL28" s="9"/>
+      <x:c r="EM28" s="9"/>
+      <x:c r="EN28" s="9"/>
       <x:c r="EO28" s="9"/>
       <x:c r="EP28" s="9"/>
       <x:c r="EQ28" s="9"/>
@@ -6231,25 +6233,25 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="9" t="str">
-        <x:v>p4f</x:v>
+        <x:v>p4e</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>ディスクレーマー共通部品</x:v>
+        <x:v>SC-04 継続記録UI</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>村上</x:v>
+        <x:v>ゆうと</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>基盤/feature</x:v>
+        <x:v>feature/sc04-record-ui</x:v>
       </x:c>
       <x:c r="F29" s="9" t="str">
-        <x:v>8/20</x:v>
+        <x:v>8/12</x:v>
       </x:c>
       <x:c r="G29" s="9" t="str">
-        <x:v>9/5</x:v>
+        <x:v>8/25</x:v>
       </x:c>
       <x:c r="H29" s="9"/>
       <x:c r="I29" s="9"/>
@@ -6323,31 +6325,31 @@
       <x:c r="BY29" s="9"/>
       <x:c r="BZ29" s="9"/>
       <x:c r="CA29" s="9"/>
-      <x:c r="CB29" s="9"/>
-      <x:c r="CC29" s="9"/>
-      <x:c r="CD29" s="9"/>
-      <x:c r="CE29" s="9"/>
-      <x:c r="CF29" s="9"/>
-      <x:c r="CG29" s="9"/>
-      <x:c r="CH29" s="9"/>
-      <x:c r="CI29" s="9"/>
+      <x:c r="CB29" s="16"/>
+      <x:c r="CC29" s="16"/>
+      <x:c r="CD29" s="16"/>
+      <x:c r="CE29" s="16"/>
+      <x:c r="CF29" s="16"/>
+      <x:c r="CG29" s="16"/>
+      <x:c r="CH29" s="16"/>
+      <x:c r="CI29" s="16"/>
       <x:c r="CJ29" s="16"/>
       <x:c r="CK29" s="16"/>
       <x:c r="CL29" s="16"/>
       <x:c r="CM29" s="16"/>
       <x:c r="CN29" s="16"/>
       <x:c r="CO29" s="16"/>
-      <x:c r="CP29" s="16"/>
-      <x:c r="CQ29" s="16"/>
-      <x:c r="CR29" s="16"/>
-      <x:c r="CS29" s="16"/>
-      <x:c r="CT29" s="16"/>
-      <x:c r="CU29" s="16"/>
-      <x:c r="CV29" s="16"/>
-      <x:c r="CW29" s="16"/>
-      <x:c r="CX29" s="16"/>
-      <x:c r="CY29" s="16"/>
-      <x:c r="CZ29" s="16"/>
+      <x:c r="CP29" s="9"/>
+      <x:c r="CQ29" s="9"/>
+      <x:c r="CR29" s="9"/>
+      <x:c r="CS29" s="9"/>
+      <x:c r="CT29" s="9"/>
+      <x:c r="CU29" s="9"/>
+      <x:c r="CV29" s="9"/>
+      <x:c r="CW29" s="9"/>
+      <x:c r="CX29" s="9"/>
+      <x:c r="CY29" s="9"/>
+      <x:c r="CZ29" s="9"/>
       <x:c r="DA29" s="9"/>
       <x:c r="DB29" s="9"/>
       <x:c r="DC29" s="9"/>
@@ -6425,7 +6427,7 @@
         <x:v>p5a</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>develop 統合・通しデモ</x:v>
+        <x:v>develop統合・通しデモ（最小MVP）</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
         <x:v>P5</x:v>
@@ -6437,10 +6439,10 @@
         <x:v>develop</x:v>
       </x:c>
       <x:c r="F30" s="9" t="str">
-        <x:v>10/16</x:v>
+        <x:v>8/22</x:v>
       </x:c>
       <x:c r="G30" s="9" t="str">
-        <x:v>10/22</x:v>
+        <x:v>8/27</x:v>
       </x:c>
       <x:c r="H30" s="9"/>
       <x:c r="I30" s="9"/>
@@ -6524,12 +6526,12 @@
       <x:c r="CI30" s="9"/>
       <x:c r="CJ30" s="9"/>
       <x:c r="CK30" s="9"/>
-      <x:c r="CL30" s="9"/>
-      <x:c r="CM30" s="9"/>
-      <x:c r="CN30" s="9"/>
-      <x:c r="CO30" s="9"/>
-      <x:c r="CP30" s="9"/>
-      <x:c r="CQ30" s="9"/>
+      <x:c r="CL30" s="16"/>
+      <x:c r="CM30" s="16"/>
+      <x:c r="CN30" s="16"/>
+      <x:c r="CO30" s="16"/>
+      <x:c r="CP30" s="16"/>
+      <x:c r="CQ30" s="16"/>
       <x:c r="CR30" s="9"/>
       <x:c r="CS30" s="9"/>
       <x:c r="CT30" s="9"/>
@@ -6579,13 +6581,13 @@
       <x:c r="EL30" s="9"/>
       <x:c r="EM30" s="9"/>
       <x:c r="EN30" s="9"/>
-      <x:c r="EO30" s="16"/>
-      <x:c r="EP30" s="16"/>
-      <x:c r="EQ30" s="16"/>
-      <x:c r="ER30" s="16"/>
-      <x:c r="ES30" s="16"/>
-      <x:c r="ET30" s="16"/>
-      <x:c r="EU30" s="16"/>
+      <x:c r="EO30" s="9"/>
+      <x:c r="EP30" s="9"/>
+      <x:c r="EQ30" s="9"/>
+      <x:c r="ER30" s="9"/>
+      <x:c r="ES30" s="9"/>
+      <x:c r="ET30" s="9"/>
+      <x:c r="EU30" s="9"/>
       <x:c r="EV30" s="9"/>
       <x:c r="EW30" s="9"/>
       <x:c r="EX30" s="9"/>
@@ -6613,25 +6615,25 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="9" t="str">
-        <x:v>p5b</x:v>
+        <x:v>p5c</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>機能/アクセシビリティテスト</x:v>
+        <x:v>薬機法表現チェック（公開前）</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
         <x:v>P5</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>村上/全員</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
         <x:v>develop</x:v>
       </x:c>
       <x:c r="F31" s="9" t="str">
-        <x:v>10/20</x:v>
+        <x:v>8/24</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
-        <x:v>10/28</x:v>
+        <x:v>8/29</x:v>
       </x:c>
       <x:c r="H31" s="9"/>
       <x:c r="I31" s="9"/>
@@ -6717,12 +6719,12 @@
       <x:c r="CK31" s="9"/>
       <x:c r="CL31" s="9"/>
       <x:c r="CM31" s="9"/>
-      <x:c r="CN31" s="9"/>
-      <x:c r="CO31" s="9"/>
-      <x:c r="CP31" s="9"/>
-      <x:c r="CQ31" s="9"/>
-      <x:c r="CR31" s="9"/>
-      <x:c r="CS31" s="9"/>
+      <x:c r="CN31" s="16"/>
+      <x:c r="CO31" s="16"/>
+      <x:c r="CP31" s="16"/>
+      <x:c r="CQ31" s="16"/>
+      <x:c r="CR31" s="16"/>
+      <x:c r="CS31" s="16"/>
       <x:c r="CT31" s="9"/>
       <x:c r="CU31" s="9"/>
       <x:c r="CV31" s="9"/>
@@ -6774,15 +6776,15 @@
       <x:c r="EP31" s="9"/>
       <x:c r="EQ31" s="9"/>
       <x:c r="ER31" s="9"/>
-      <x:c r="ES31" s="16"/>
-      <x:c r="ET31" s="16"/>
-      <x:c r="EU31" s="16"/>
-      <x:c r="EV31" s="16"/>
-      <x:c r="EW31" s="16"/>
-      <x:c r="EX31" s="16"/>
-      <x:c r="EY31" s="16"/>
-      <x:c r="EZ31" s="16"/>
-      <x:c r="FA31" s="16"/>
+      <x:c r="ES31" s="9"/>
+      <x:c r="ET31" s="9"/>
+      <x:c r="EU31" s="9"/>
+      <x:c r="EV31" s="9"/>
+      <x:c r="EW31" s="9"/>
+      <x:c r="EX31" s="9"/>
+      <x:c r="EY31" s="9"/>
+      <x:c r="EZ31" s="9"/>
+      <x:c r="FA31" s="9"/>
       <x:c r="FB31" s="9"/>
       <x:c r="FC31" s="9"/>
       <x:c r="FD31" s="9"/>
@@ -6804,25 +6806,25 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="9" t="str">
-        <x:v>p5c</x:v>
+        <x:v>p5d</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>薬機法表現チェック</x:v>
+        <x:v>最小MVP Web公開（GitHub Pages）</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
         <x:v>P5</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>たかと</x:v>
+        <x:v>村上</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
         <x:v>develop</x:v>
       </x:c>
       <x:c r="F32" s="9" t="str">
-        <x:v>10/22</x:v>
+        <x:v>8/27</x:v>
       </x:c>
       <x:c r="G32" s="9" t="str">
-        <x:v>10/31</x:v>
+        <x:v>8/31</x:v>
       </x:c>
       <x:c r="H32" s="9"/>
       <x:c r="I32" s="9"/>
@@ -6911,11 +6913,11 @@
       <x:c r="CN32" s="9"/>
       <x:c r="CO32" s="9"/>
       <x:c r="CP32" s="9"/>
-      <x:c r="CQ32" s="9"/>
-      <x:c r="CR32" s="9"/>
-      <x:c r="CS32" s="9"/>
-      <x:c r="CT32" s="9"/>
-      <x:c r="CU32" s="9"/>
+      <x:c r="CQ32" s="16"/>
+      <x:c r="CR32" s="16"/>
+      <x:c r="CS32" s="16"/>
+      <x:c r="CT32" s="16"/>
+      <x:c r="CU32" s="16"/>
       <x:c r="CV32" s="9"/>
       <x:c r="CW32" s="9"/>
       <x:c r="CX32" s="9"/>
@@ -6967,16 +6969,16 @@
       <x:c r="ER32" s="9"/>
       <x:c r="ES32" s="9"/>
       <x:c r="ET32" s="9"/>
-      <x:c r="EU32" s="16"/>
-      <x:c r="EV32" s="16"/>
-      <x:c r="EW32" s="16"/>
-      <x:c r="EX32" s="16"/>
-      <x:c r="EY32" s="16"/>
-      <x:c r="EZ32" s="16"/>
-      <x:c r="FA32" s="16"/>
-      <x:c r="FB32" s="16"/>
-      <x:c r="FC32" s="16"/>
-      <x:c r="FD32" s="16"/>
+      <x:c r="EU32" s="9"/>
+      <x:c r="EV32" s="9"/>
+      <x:c r="EW32" s="9"/>
+      <x:c r="EX32" s="9"/>
+      <x:c r="EY32" s="9"/>
+      <x:c r="EZ32" s="9"/>
+      <x:c r="FA32" s="9"/>
+      <x:c r="FB32" s="9"/>
+      <x:c r="FC32" s="9"/>
+      <x:c r="FD32" s="9"/>
       <x:c r="FE32" s="9"/>
       <x:c r="FF32" s="9"/>
       <x:c r="FG32" s="9"/>
@@ -6995,13 +6997,13 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="9" t="str">
-        <x:v>p6a</x:v>
+        <x:v>m_mvp</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>デモシナリオ・発表資料</x:v>
+        <x:v>★ M-MVP 最小アプリ Web公開（8月末・WEB動作）</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>P6</x:v>
+        <x:v>M</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
         <x:v>全員</x:v>
@@ -7010,10 +7012,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F33" s="9" t="str">
-        <x:v>11/1</x:v>
+        <x:v>8/31</x:v>
       </x:c>
       <x:c r="G33" s="9" t="str">
-        <x:v>11/10</x:v>
+        <x:v>8/31</x:v>
       </x:c>
       <x:c r="H33" s="9"/>
       <x:c r="I33" s="9"/>
@@ -7106,7 +7108,9 @@
       <x:c r="CR33" s="9"/>
       <x:c r="CS33" s="9"/>
       <x:c r="CT33" s="9"/>
-      <x:c r="CU33" s="9"/>
+      <x:c r="CU33" s="20" t="str">
+        <x:v>◆</x:v>
+      </x:c>
       <x:c r="CV33" s="9"/>
       <x:c r="CW33" s="9"/>
       <x:c r="CX33" s="9"/>
@@ -7168,16 +7172,16 @@
       <x:c r="FB33" s="9"/>
       <x:c r="FC33" s="9"/>
       <x:c r="FD33" s="9"/>
-      <x:c r="FE33" s="16"/>
-      <x:c r="FF33" s="16"/>
-      <x:c r="FG33" s="16"/>
-      <x:c r="FH33" s="16"/>
-      <x:c r="FI33" s="16"/>
-      <x:c r="FJ33" s="16"/>
-      <x:c r="FK33" s="16"/>
-      <x:c r="FL33" s="16"/>
-      <x:c r="FM33" s="16"/>
-      <x:c r="FN33" s="16"/>
+      <x:c r="FE33" s="9"/>
+      <x:c r="FF33" s="9"/>
+      <x:c r="FG33" s="9"/>
+      <x:c r="FH33" s="9"/>
+      <x:c r="FI33" s="9"/>
+      <x:c r="FJ33" s="9"/>
+      <x:c r="FK33" s="9"/>
+      <x:c r="FL33" s="9"/>
+      <x:c r="FM33" s="9"/>
+      <x:c r="FN33" s="9"/>
       <x:c r="FO33" s="9"/>
       <x:c r="FP33" s="9"/>
       <x:c r="FQ33" s="9"/>
@@ -7185,26 +7189,26 @@
       <x:c r="FS33" s="9"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="9" t="str">
-        <x:v>p6b</x:v>
-      </x:c>
-      <x:c r="B34" s="9" t="str">
-        <x:v>リハーサル・最終調整</x:v>
-      </x:c>
-      <x:c r="C34" s="9" t="str">
-        <x:v>P6</x:v>
-      </x:c>
-      <x:c r="D34" s="9" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E34" s="9" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F34" s="9" t="str">
-        <x:v>11/8</x:v>
-      </x:c>
-      <x:c r="G34" s="9" t="str">
-        <x:v>11/15</x:v>
+      <x:c r="A34" s="18" t="str">
+        <x:v>p2b</x:v>
+      </x:c>
+      <x:c r="B34" s="18" t="str">
+        <x:v>Supabase連携（最小MVP後・拡張）</x:v>
+      </x:c>
+      <x:c r="C34" s="18" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="str">
+        <x:v>村上/ひろと</x:v>
+      </x:c>
+      <x:c r="E34" s="18" t="str">
+        <x:v>基盤</x:v>
+      </x:c>
+      <x:c r="F34" s="18" t="str">
+        <x:v>9/1</x:v>
+      </x:c>
+      <x:c r="G34" s="18" t="str">
+        <x:v>9/15</x:v>
       </x:c>
       <x:c r="H34" s="9"/>
       <x:c r="I34" s="9"/>
@@ -7298,21 +7302,21 @@
       <x:c r="CS34" s="9"/>
       <x:c r="CT34" s="9"/>
       <x:c r="CU34" s="9"/>
-      <x:c r="CV34" s="9"/>
-      <x:c r="CW34" s="9"/>
-      <x:c r="CX34" s="9"/>
-      <x:c r="CY34" s="9"/>
-      <x:c r="CZ34" s="9"/>
-      <x:c r="DA34" s="9"/>
-      <x:c r="DB34" s="9"/>
-      <x:c r="DC34" s="9"/>
-      <x:c r="DD34" s="9"/>
-      <x:c r="DE34" s="9"/>
-      <x:c r="DF34" s="9"/>
-      <x:c r="DG34" s="9"/>
-      <x:c r="DH34" s="9"/>
-      <x:c r="DI34" s="9"/>
-      <x:c r="DJ34" s="9"/>
+      <x:c r="CV34" s="16"/>
+      <x:c r="CW34" s="16"/>
+      <x:c r="CX34" s="16"/>
+      <x:c r="CY34" s="16"/>
+      <x:c r="CZ34" s="16"/>
+      <x:c r="DA34" s="16"/>
+      <x:c r="DB34" s="16"/>
+      <x:c r="DC34" s="16"/>
+      <x:c r="DD34" s="16"/>
+      <x:c r="DE34" s="16"/>
+      <x:c r="DF34" s="16"/>
+      <x:c r="DG34" s="16"/>
+      <x:c r="DH34" s="16"/>
+      <x:c r="DI34" s="16"/>
+      <x:c r="DJ34" s="16"/>
       <x:c r="DK34" s="9"/>
       <x:c r="DL34" s="9"/>
       <x:c r="DM34" s="9"/>
@@ -7366,36 +7370,36 @@
       <x:c r="FI34" s="9"/>
       <x:c r="FJ34" s="9"/>
       <x:c r="FK34" s="9"/>
-      <x:c r="FL34" s="16"/>
-      <x:c r="FM34" s="16"/>
-      <x:c r="FN34" s="16"/>
-      <x:c r="FO34" s="16"/>
-      <x:c r="FP34" s="16"/>
-      <x:c r="FQ34" s="16"/>
-      <x:c r="FR34" s="16"/>
-      <x:c r="FS34" s="16"/>
+      <x:c r="FL34" s="9"/>
+      <x:c r="FM34" s="9"/>
+      <x:c r="FN34" s="9"/>
+      <x:c r="FO34" s="9"/>
+      <x:c r="FP34" s="9"/>
+      <x:c r="FQ34" s="9"/>
+      <x:c r="FR34" s="9"/>
+      <x:c r="FS34" s="9"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="9" t="str">
-        <x:v>mbase</x:v>
+        <x:v>p3d</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>★ M-Base 基盤アプリ完成（developマージ）</x:v>
+        <x:v>商品マスター拡充(30-50)</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>M</x:v>
+        <x:v>P3</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>村上</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>基盤</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="F35" s="9" t="str">
-        <x:v>7/31</x:v>
+        <x:v>9/1</x:v>
       </x:c>
       <x:c r="G35" s="9" t="str">
-        <x:v>7/31</x:v>
+        <x:v>9/25</x:v>
       </x:c>
       <x:c r="H35" s="9"/>
       <x:c r="I35" s="9"/>
@@ -7457,9 +7461,7 @@
       <x:c r="BM35" s="9"/>
       <x:c r="BN35" s="9"/>
       <x:c r="BO35" s="9"/>
-      <x:c r="BP35" s="20" t="str">
-        <x:v>◆</x:v>
-      </x:c>
+      <x:c r="BP35" s="9"/>
       <x:c r="BQ35" s="9"/>
       <x:c r="BR35" s="9"/>
       <x:c r="BS35" s="9"/>
@@ -7491,31 +7493,31 @@
       <x:c r="CS35" s="9"/>
       <x:c r="CT35" s="9"/>
       <x:c r="CU35" s="9"/>
-      <x:c r="CV35" s="9"/>
-      <x:c r="CW35" s="9"/>
-      <x:c r="CX35" s="9"/>
-      <x:c r="CY35" s="9"/>
-      <x:c r="CZ35" s="9"/>
-      <x:c r="DA35" s="9"/>
-      <x:c r="DB35" s="9"/>
-      <x:c r="DC35" s="9"/>
-      <x:c r="DD35" s="9"/>
-      <x:c r="DE35" s="9"/>
-      <x:c r="DF35" s="9"/>
-      <x:c r="DG35" s="9"/>
-      <x:c r="DH35" s="9"/>
-      <x:c r="DI35" s="9"/>
-      <x:c r="DJ35" s="9"/>
-      <x:c r="DK35" s="9"/>
-      <x:c r="DL35" s="9"/>
-      <x:c r="DM35" s="9"/>
-      <x:c r="DN35" s="9"/>
-      <x:c r="DO35" s="9"/>
-      <x:c r="DP35" s="9"/>
-      <x:c r="DQ35" s="9"/>
-      <x:c r="DR35" s="9"/>
-      <x:c r="DS35" s="9"/>
-      <x:c r="DT35" s="9"/>
+      <x:c r="CV35" s="16"/>
+      <x:c r="CW35" s="16"/>
+      <x:c r="CX35" s="16"/>
+      <x:c r="CY35" s="16"/>
+      <x:c r="CZ35" s="16"/>
+      <x:c r="DA35" s="16"/>
+      <x:c r="DB35" s="16"/>
+      <x:c r="DC35" s="16"/>
+      <x:c r="DD35" s="16"/>
+      <x:c r="DE35" s="16"/>
+      <x:c r="DF35" s="16"/>
+      <x:c r="DG35" s="16"/>
+      <x:c r="DH35" s="16"/>
+      <x:c r="DI35" s="16"/>
+      <x:c r="DJ35" s="16"/>
+      <x:c r="DK35" s="16"/>
+      <x:c r="DL35" s="16"/>
+      <x:c r="DM35" s="16"/>
+      <x:c r="DN35" s="16"/>
+      <x:c r="DO35" s="16"/>
+      <x:c r="DP35" s="16"/>
+      <x:c r="DQ35" s="16"/>
+      <x:c r="DR35" s="16"/>
+      <x:c r="DS35" s="16"/>
+      <x:c r="DT35" s="16"/>
       <x:c r="DU35" s="9"/>
       <x:c r="DV35" s="9"/>
       <x:c r="DW35" s="9"/>
@@ -7570,25 +7572,25 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="9" t="str">
-        <x:v>m1</x:v>
+        <x:v>p5b</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>★ 中間発表（マイルストーン）</x:v>
+        <x:v>機能/アクセシビリティテスト</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>M</x:v>
+        <x:v>P5</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>全員</x:v>
+        <x:v>村上/全員</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>—</x:v>
+        <x:v>develop</x:v>
       </x:c>
       <x:c r="F36" s="9" t="str">
-        <x:v>11/15</x:v>
+        <x:v>10/1</x:v>
       </x:c>
       <x:c r="G36" s="9" t="str">
-        <x:v>11/15</x:v>
+        <x:v>10/22</x:v>
       </x:c>
       <x:c r="H36" s="9"/>
       <x:c r="I36" s="9"/>
@@ -7712,28 +7714,28 @@
       <x:c r="DW36" s="9"/>
       <x:c r="DX36" s="9"/>
       <x:c r="DY36" s="9"/>
-      <x:c r="DZ36" s="9"/>
-      <x:c r="EA36" s="9"/>
-      <x:c r="EB36" s="9"/>
-      <x:c r="EC36" s="9"/>
-      <x:c r="ED36" s="9"/>
-      <x:c r="EE36" s="9"/>
-      <x:c r="EF36" s="9"/>
-      <x:c r="EG36" s="9"/>
-      <x:c r="EH36" s="9"/>
-      <x:c r="EI36" s="9"/>
-      <x:c r="EJ36" s="9"/>
-      <x:c r="EK36" s="9"/>
-      <x:c r="EL36" s="9"/>
-      <x:c r="EM36" s="9"/>
-      <x:c r="EN36" s="9"/>
-      <x:c r="EO36" s="9"/>
-      <x:c r="EP36" s="9"/>
-      <x:c r="EQ36" s="9"/>
-      <x:c r="ER36" s="9"/>
-      <x:c r="ES36" s="9"/>
-      <x:c r="ET36" s="9"/>
-      <x:c r="EU36" s="9"/>
+      <x:c r="DZ36" s="16"/>
+      <x:c r="EA36" s="16"/>
+      <x:c r="EB36" s="16"/>
+      <x:c r="EC36" s="16"/>
+      <x:c r="ED36" s="16"/>
+      <x:c r="EE36" s="16"/>
+      <x:c r="EF36" s="16"/>
+      <x:c r="EG36" s="16"/>
+      <x:c r="EH36" s="16"/>
+      <x:c r="EI36" s="16"/>
+      <x:c r="EJ36" s="16"/>
+      <x:c r="EK36" s="16"/>
+      <x:c r="EL36" s="16"/>
+      <x:c r="EM36" s="16"/>
+      <x:c r="EN36" s="16"/>
+      <x:c r="EO36" s="16"/>
+      <x:c r="EP36" s="16"/>
+      <x:c r="EQ36" s="16"/>
+      <x:c r="ER36" s="16"/>
+      <x:c r="ES36" s="16"/>
+      <x:c r="ET36" s="16"/>
+      <x:c r="EU36" s="16"/>
       <x:c r="EV36" s="9"/>
       <x:c r="EW36" s="9"/>
       <x:c r="EX36" s="9"/>
@@ -7757,7 +7759,580 @@
       <x:c r="FP36" s="9"/>
       <x:c r="FQ36" s="9"/>
       <x:c r="FR36" s="9"/>
-      <x:c r="FS36" s="20" t="str">
+      <x:c r="FS36" s="9"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="9" t="str">
+        <x:v>p6a</x:v>
+      </x:c>
+      <x:c r="B37" s="9" t="str">
+        <x:v>デモシナリオ・発表資料</x:v>
+      </x:c>
+      <x:c r="C37" s="9" t="str">
+        <x:v>P6</x:v>
+      </x:c>
+      <x:c r="D37" s="9" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="E37" s="9" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F37" s="9" t="str">
+        <x:v>11/1</x:v>
+      </x:c>
+      <x:c r="G37" s="9" t="str">
+        <x:v>11/10</x:v>
+      </x:c>
+      <x:c r="H37" s="9"/>
+      <x:c r="I37" s="9"/>
+      <x:c r="J37" s="9"/>
+      <x:c r="K37" s="9"/>
+      <x:c r="L37" s="9"/>
+      <x:c r="M37" s="9"/>
+      <x:c r="N37" s="9"/>
+      <x:c r="O37" s="9"/>
+      <x:c r="P37" s="9"/>
+      <x:c r="Q37" s="9"/>
+      <x:c r="R37" s="9"/>
+      <x:c r="S37" s="9"/>
+      <x:c r="T37" s="9"/>
+      <x:c r="U37" s="9"/>
+      <x:c r="V37" s="9"/>
+      <x:c r="W37" s="9"/>
+      <x:c r="X37" s="9"/>
+      <x:c r="Y37" s="9"/>
+      <x:c r="Z37" s="9"/>
+      <x:c r="AA37" s="9"/>
+      <x:c r="AB37" s="9"/>
+      <x:c r="AC37" s="9"/>
+      <x:c r="AD37" s="9"/>
+      <x:c r="AE37" s="9"/>
+      <x:c r="AF37" s="9"/>
+      <x:c r="AG37" s="9"/>
+      <x:c r="AH37" s="9"/>
+      <x:c r="AI37" s="9"/>
+      <x:c r="AJ37" s="9"/>
+      <x:c r="AK37" s="9"/>
+      <x:c r="AL37" s="9"/>
+      <x:c r="AM37" s="9"/>
+      <x:c r="AN37" s="9"/>
+      <x:c r="AO37" s="9"/>
+      <x:c r="AP37" s="9"/>
+      <x:c r="AQ37" s="9"/>
+      <x:c r="AR37" s="9"/>
+      <x:c r="AS37" s="9"/>
+      <x:c r="AT37" s="9"/>
+      <x:c r="AU37" s="9"/>
+      <x:c r="AV37" s="9"/>
+      <x:c r="AW37" s="9"/>
+      <x:c r="AX37" s="9"/>
+      <x:c r="AY37" s="9"/>
+      <x:c r="AZ37" s="9"/>
+      <x:c r="BA37" s="9"/>
+      <x:c r="BB37" s="9"/>
+      <x:c r="BC37" s="9"/>
+      <x:c r="BD37" s="9"/>
+      <x:c r="BE37" s="9"/>
+      <x:c r="BF37" s="9"/>
+      <x:c r="BG37" s="9"/>
+      <x:c r="BH37" s="9"/>
+      <x:c r="BI37" s="9"/>
+      <x:c r="BJ37" s="9"/>
+      <x:c r="BK37" s="9"/>
+      <x:c r="BL37" s="9"/>
+      <x:c r="BM37" s="9"/>
+      <x:c r="BN37" s="9"/>
+      <x:c r="BO37" s="9"/>
+      <x:c r="BP37" s="9"/>
+      <x:c r="BQ37" s="9"/>
+      <x:c r="BR37" s="9"/>
+      <x:c r="BS37" s="9"/>
+      <x:c r="BT37" s="9"/>
+      <x:c r="BU37" s="9"/>
+      <x:c r="BV37" s="9"/>
+      <x:c r="BW37" s="9"/>
+      <x:c r="BX37" s="9"/>
+      <x:c r="BY37" s="9"/>
+      <x:c r="BZ37" s="9"/>
+      <x:c r="CA37" s="9"/>
+      <x:c r="CB37" s="9"/>
+      <x:c r="CC37" s="9"/>
+      <x:c r="CD37" s="9"/>
+      <x:c r="CE37" s="9"/>
+      <x:c r="CF37" s="9"/>
+      <x:c r="CG37" s="9"/>
+      <x:c r="CH37" s="9"/>
+      <x:c r="CI37" s="9"/>
+      <x:c r="CJ37" s="9"/>
+      <x:c r="CK37" s="9"/>
+      <x:c r="CL37" s="9"/>
+      <x:c r="CM37" s="9"/>
+      <x:c r="CN37" s="9"/>
+      <x:c r="CO37" s="9"/>
+      <x:c r="CP37" s="9"/>
+      <x:c r="CQ37" s="9"/>
+      <x:c r="CR37" s="9"/>
+      <x:c r="CS37" s="9"/>
+      <x:c r="CT37" s="9"/>
+      <x:c r="CU37" s="9"/>
+      <x:c r="CV37" s="9"/>
+      <x:c r="CW37" s="9"/>
+      <x:c r="CX37" s="9"/>
+      <x:c r="CY37" s="9"/>
+      <x:c r="CZ37" s="9"/>
+      <x:c r="DA37" s="9"/>
+      <x:c r="DB37" s="9"/>
+      <x:c r="DC37" s="9"/>
+      <x:c r="DD37" s="9"/>
+      <x:c r="DE37" s="9"/>
+      <x:c r="DF37" s="9"/>
+      <x:c r="DG37" s="9"/>
+      <x:c r="DH37" s="9"/>
+      <x:c r="DI37" s="9"/>
+      <x:c r="DJ37" s="9"/>
+      <x:c r="DK37" s="9"/>
+      <x:c r="DL37" s="9"/>
+      <x:c r="DM37" s="9"/>
+      <x:c r="DN37" s="9"/>
+      <x:c r="DO37" s="9"/>
+      <x:c r="DP37" s="9"/>
+      <x:c r="DQ37" s="9"/>
+      <x:c r="DR37" s="9"/>
+      <x:c r="DS37" s="9"/>
+      <x:c r="DT37" s="9"/>
+      <x:c r="DU37" s="9"/>
+      <x:c r="DV37" s="9"/>
+      <x:c r="DW37" s="9"/>
+      <x:c r="DX37" s="9"/>
+      <x:c r="DY37" s="9"/>
+      <x:c r="DZ37" s="9"/>
+      <x:c r="EA37" s="9"/>
+      <x:c r="EB37" s="9"/>
+      <x:c r="EC37" s="9"/>
+      <x:c r="ED37" s="9"/>
+      <x:c r="EE37" s="9"/>
+      <x:c r="EF37" s="9"/>
+      <x:c r="EG37" s="9"/>
+      <x:c r="EH37" s="9"/>
+      <x:c r="EI37" s="9"/>
+      <x:c r="EJ37" s="9"/>
+      <x:c r="EK37" s="9"/>
+      <x:c r="EL37" s="9"/>
+      <x:c r="EM37" s="9"/>
+      <x:c r="EN37" s="9"/>
+      <x:c r="EO37" s="9"/>
+      <x:c r="EP37" s="9"/>
+      <x:c r="EQ37" s="9"/>
+      <x:c r="ER37" s="9"/>
+      <x:c r="ES37" s="9"/>
+      <x:c r="ET37" s="9"/>
+      <x:c r="EU37" s="9"/>
+      <x:c r="EV37" s="9"/>
+      <x:c r="EW37" s="9"/>
+      <x:c r="EX37" s="9"/>
+      <x:c r="EY37" s="9"/>
+      <x:c r="EZ37" s="9"/>
+      <x:c r="FA37" s="9"/>
+      <x:c r="FB37" s="9"/>
+      <x:c r="FC37" s="9"/>
+      <x:c r="FD37" s="9"/>
+      <x:c r="FE37" s="16"/>
+      <x:c r="FF37" s="16"/>
+      <x:c r="FG37" s="16"/>
+      <x:c r="FH37" s="16"/>
+      <x:c r="FI37" s="16"/>
+      <x:c r="FJ37" s="16"/>
+      <x:c r="FK37" s="16"/>
+      <x:c r="FL37" s="16"/>
+      <x:c r="FM37" s="16"/>
+      <x:c r="FN37" s="16"/>
+      <x:c r="FO37" s="9"/>
+      <x:c r="FP37" s="9"/>
+      <x:c r="FQ37" s="9"/>
+      <x:c r="FR37" s="9"/>
+      <x:c r="FS37" s="9"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="9" t="str">
+        <x:v>p6b</x:v>
+      </x:c>
+      <x:c r="B38" s="9" t="str">
+        <x:v>リハーサル・最終調整</x:v>
+      </x:c>
+      <x:c r="C38" s="9" t="str">
+        <x:v>P6</x:v>
+      </x:c>
+      <x:c r="D38" s="9" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="E38" s="9" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F38" s="9" t="str">
+        <x:v>11/8</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="str">
+        <x:v>11/15</x:v>
+      </x:c>
+      <x:c r="H38" s="9"/>
+      <x:c r="I38" s="9"/>
+      <x:c r="J38" s="9"/>
+      <x:c r="K38" s="9"/>
+      <x:c r="L38" s="9"/>
+      <x:c r="M38" s="9"/>
+      <x:c r="N38" s="9"/>
+      <x:c r="O38" s="9"/>
+      <x:c r="P38" s="9"/>
+      <x:c r="Q38" s="9"/>
+      <x:c r="R38" s="9"/>
+      <x:c r="S38" s="9"/>
+      <x:c r="T38" s="9"/>
+      <x:c r="U38" s="9"/>
+      <x:c r="V38" s="9"/>
+      <x:c r="W38" s="9"/>
+      <x:c r="X38" s="9"/>
+      <x:c r="Y38" s="9"/>
+      <x:c r="Z38" s="9"/>
+      <x:c r="AA38" s="9"/>
+      <x:c r="AB38" s="9"/>
+      <x:c r="AC38" s="9"/>
+      <x:c r="AD38" s="9"/>
+      <x:c r="AE38" s="9"/>
+      <x:c r="AF38" s="9"/>
+      <x:c r="AG38" s="9"/>
+      <x:c r="AH38" s="9"/>
+      <x:c r="AI38" s="9"/>
+      <x:c r="AJ38" s="9"/>
+      <x:c r="AK38" s="9"/>
+      <x:c r="AL38" s="9"/>
+      <x:c r="AM38" s="9"/>
+      <x:c r="AN38" s="9"/>
+      <x:c r="AO38" s="9"/>
+      <x:c r="AP38" s="9"/>
+      <x:c r="AQ38" s="9"/>
+      <x:c r="AR38" s="9"/>
+      <x:c r="AS38" s="9"/>
+      <x:c r="AT38" s="9"/>
+      <x:c r="AU38" s="9"/>
+      <x:c r="AV38" s="9"/>
+      <x:c r="AW38" s="9"/>
+      <x:c r="AX38" s="9"/>
+      <x:c r="AY38" s="9"/>
+      <x:c r="AZ38" s="9"/>
+      <x:c r="BA38" s="9"/>
+      <x:c r="BB38" s="9"/>
+      <x:c r="BC38" s="9"/>
+      <x:c r="BD38" s="9"/>
+      <x:c r="BE38" s="9"/>
+      <x:c r="BF38" s="9"/>
+      <x:c r="BG38" s="9"/>
+      <x:c r="BH38" s="9"/>
+      <x:c r="BI38" s="9"/>
+      <x:c r="BJ38" s="9"/>
+      <x:c r="BK38" s="9"/>
+      <x:c r="BL38" s="9"/>
+      <x:c r="BM38" s="9"/>
+      <x:c r="BN38" s="9"/>
+      <x:c r="BO38" s="9"/>
+      <x:c r="BP38" s="9"/>
+      <x:c r="BQ38" s="9"/>
+      <x:c r="BR38" s="9"/>
+      <x:c r="BS38" s="9"/>
+      <x:c r="BT38" s="9"/>
+      <x:c r="BU38" s="9"/>
+      <x:c r="BV38" s="9"/>
+      <x:c r="BW38" s="9"/>
+      <x:c r="BX38" s="9"/>
+      <x:c r="BY38" s="9"/>
+      <x:c r="BZ38" s="9"/>
+      <x:c r="CA38" s="9"/>
+      <x:c r="CB38" s="9"/>
+      <x:c r="CC38" s="9"/>
+      <x:c r="CD38" s="9"/>
+      <x:c r="CE38" s="9"/>
+      <x:c r="CF38" s="9"/>
+      <x:c r="CG38" s="9"/>
+      <x:c r="CH38" s="9"/>
+      <x:c r="CI38" s="9"/>
+      <x:c r="CJ38" s="9"/>
+      <x:c r="CK38" s="9"/>
+      <x:c r="CL38" s="9"/>
+      <x:c r="CM38" s="9"/>
+      <x:c r="CN38" s="9"/>
+      <x:c r="CO38" s="9"/>
+      <x:c r="CP38" s="9"/>
+      <x:c r="CQ38" s="9"/>
+      <x:c r="CR38" s="9"/>
+      <x:c r="CS38" s="9"/>
+      <x:c r="CT38" s="9"/>
+      <x:c r="CU38" s="9"/>
+      <x:c r="CV38" s="9"/>
+      <x:c r="CW38" s="9"/>
+      <x:c r="CX38" s="9"/>
+      <x:c r="CY38" s="9"/>
+      <x:c r="CZ38" s="9"/>
+      <x:c r="DA38" s="9"/>
+      <x:c r="DB38" s="9"/>
+      <x:c r="DC38" s="9"/>
+      <x:c r="DD38" s="9"/>
+      <x:c r="DE38" s="9"/>
+      <x:c r="DF38" s="9"/>
+      <x:c r="DG38" s="9"/>
+      <x:c r="DH38" s="9"/>
+      <x:c r="DI38" s="9"/>
+      <x:c r="DJ38" s="9"/>
+      <x:c r="DK38" s="9"/>
+      <x:c r="DL38" s="9"/>
+      <x:c r="DM38" s="9"/>
+      <x:c r="DN38" s="9"/>
+      <x:c r="DO38" s="9"/>
+      <x:c r="DP38" s="9"/>
+      <x:c r="DQ38" s="9"/>
+      <x:c r="DR38" s="9"/>
+      <x:c r="DS38" s="9"/>
+      <x:c r="DT38" s="9"/>
+      <x:c r="DU38" s="9"/>
+      <x:c r="DV38" s="9"/>
+      <x:c r="DW38" s="9"/>
+      <x:c r="DX38" s="9"/>
+      <x:c r="DY38" s="9"/>
+      <x:c r="DZ38" s="9"/>
+      <x:c r="EA38" s="9"/>
+      <x:c r="EB38" s="9"/>
+      <x:c r="EC38" s="9"/>
+      <x:c r="ED38" s="9"/>
+      <x:c r="EE38" s="9"/>
+      <x:c r="EF38" s="9"/>
+      <x:c r="EG38" s="9"/>
+      <x:c r="EH38" s="9"/>
+      <x:c r="EI38" s="9"/>
+      <x:c r="EJ38" s="9"/>
+      <x:c r="EK38" s="9"/>
+      <x:c r="EL38" s="9"/>
+      <x:c r="EM38" s="9"/>
+      <x:c r="EN38" s="9"/>
+      <x:c r="EO38" s="9"/>
+      <x:c r="EP38" s="9"/>
+      <x:c r="EQ38" s="9"/>
+      <x:c r="ER38" s="9"/>
+      <x:c r="ES38" s="9"/>
+      <x:c r="ET38" s="9"/>
+      <x:c r="EU38" s="9"/>
+      <x:c r="EV38" s="9"/>
+      <x:c r="EW38" s="9"/>
+      <x:c r="EX38" s="9"/>
+      <x:c r="EY38" s="9"/>
+      <x:c r="EZ38" s="9"/>
+      <x:c r="FA38" s="9"/>
+      <x:c r="FB38" s="9"/>
+      <x:c r="FC38" s="9"/>
+      <x:c r="FD38" s="9"/>
+      <x:c r="FE38" s="9"/>
+      <x:c r="FF38" s="9"/>
+      <x:c r="FG38" s="9"/>
+      <x:c r="FH38" s="9"/>
+      <x:c r="FI38" s="9"/>
+      <x:c r="FJ38" s="9"/>
+      <x:c r="FK38" s="9"/>
+      <x:c r="FL38" s="16"/>
+      <x:c r="FM38" s="16"/>
+      <x:c r="FN38" s="16"/>
+      <x:c r="FO38" s="16"/>
+      <x:c r="FP38" s="16"/>
+      <x:c r="FQ38" s="16"/>
+      <x:c r="FR38" s="16"/>
+      <x:c r="FS38" s="16"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="9" t="str">
+        <x:v>m1</x:v>
+      </x:c>
+      <x:c r="B39" s="9" t="str">
+        <x:v>★ 中間発表（マイルストーン）</x:v>
+      </x:c>
+      <x:c r="C39" s="9" t="str">
+        <x:v>M</x:v>
+      </x:c>
+      <x:c r="D39" s="9" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="E39" s="9" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F39" s="9" t="str">
+        <x:v>11/15</x:v>
+      </x:c>
+      <x:c r="G39" s="9" t="str">
+        <x:v>11/15</x:v>
+      </x:c>
+      <x:c r="H39" s="9"/>
+      <x:c r="I39" s="9"/>
+      <x:c r="J39" s="9"/>
+      <x:c r="K39" s="9"/>
+      <x:c r="L39" s="9"/>
+      <x:c r="M39" s="9"/>
+      <x:c r="N39" s="9"/>
+      <x:c r="O39" s="9"/>
+      <x:c r="P39" s="9"/>
+      <x:c r="Q39" s="9"/>
+      <x:c r="R39" s="9"/>
+      <x:c r="S39" s="9"/>
+      <x:c r="T39" s="9"/>
+      <x:c r="U39" s="9"/>
+      <x:c r="V39" s="9"/>
+      <x:c r="W39" s="9"/>
+      <x:c r="X39" s="9"/>
+      <x:c r="Y39" s="9"/>
+      <x:c r="Z39" s="9"/>
+      <x:c r="AA39" s="9"/>
+      <x:c r="AB39" s="9"/>
+      <x:c r="AC39" s="9"/>
+      <x:c r="AD39" s="9"/>
+      <x:c r="AE39" s="9"/>
+      <x:c r="AF39" s="9"/>
+      <x:c r="AG39" s="9"/>
+      <x:c r="AH39" s="9"/>
+      <x:c r="AI39" s="9"/>
+      <x:c r="AJ39" s="9"/>
+      <x:c r="AK39" s="9"/>
+      <x:c r="AL39" s="9"/>
+      <x:c r="AM39" s="9"/>
+      <x:c r="AN39" s="9"/>
+      <x:c r="AO39" s="9"/>
+      <x:c r="AP39" s="9"/>
+      <x:c r="AQ39" s="9"/>
+      <x:c r="AR39" s="9"/>
+      <x:c r="AS39" s="9"/>
+      <x:c r="AT39" s="9"/>
+      <x:c r="AU39" s="9"/>
+      <x:c r="AV39" s="9"/>
+      <x:c r="AW39" s="9"/>
+      <x:c r="AX39" s="9"/>
+      <x:c r="AY39" s="9"/>
+      <x:c r="AZ39" s="9"/>
+      <x:c r="BA39" s="9"/>
+      <x:c r="BB39" s="9"/>
+      <x:c r="BC39" s="9"/>
+      <x:c r="BD39" s="9"/>
+      <x:c r="BE39" s="9"/>
+      <x:c r="BF39" s="9"/>
+      <x:c r="BG39" s="9"/>
+      <x:c r="BH39" s="9"/>
+      <x:c r="BI39" s="9"/>
+      <x:c r="BJ39" s="9"/>
+      <x:c r="BK39" s="9"/>
+      <x:c r="BL39" s="9"/>
+      <x:c r="BM39" s="9"/>
+      <x:c r="BN39" s="9"/>
+      <x:c r="BO39" s="9"/>
+      <x:c r="BP39" s="9"/>
+      <x:c r="BQ39" s="9"/>
+      <x:c r="BR39" s="9"/>
+      <x:c r="BS39" s="9"/>
+      <x:c r="BT39" s="9"/>
+      <x:c r="BU39" s="9"/>
+      <x:c r="BV39" s="9"/>
+      <x:c r="BW39" s="9"/>
+      <x:c r="BX39" s="9"/>
+      <x:c r="BY39" s="9"/>
+      <x:c r="BZ39" s="9"/>
+      <x:c r="CA39" s="9"/>
+      <x:c r="CB39" s="9"/>
+      <x:c r="CC39" s="9"/>
+      <x:c r="CD39" s="9"/>
+      <x:c r="CE39" s="9"/>
+      <x:c r="CF39" s="9"/>
+      <x:c r="CG39" s="9"/>
+      <x:c r="CH39" s="9"/>
+      <x:c r="CI39" s="9"/>
+      <x:c r="CJ39" s="9"/>
+      <x:c r="CK39" s="9"/>
+      <x:c r="CL39" s="9"/>
+      <x:c r="CM39" s="9"/>
+      <x:c r="CN39" s="9"/>
+      <x:c r="CO39" s="9"/>
+      <x:c r="CP39" s="9"/>
+      <x:c r="CQ39" s="9"/>
+      <x:c r="CR39" s="9"/>
+      <x:c r="CS39" s="9"/>
+      <x:c r="CT39" s="9"/>
+      <x:c r="CU39" s="9"/>
+      <x:c r="CV39" s="9"/>
+      <x:c r="CW39" s="9"/>
+      <x:c r="CX39" s="9"/>
+      <x:c r="CY39" s="9"/>
+      <x:c r="CZ39" s="9"/>
+      <x:c r="DA39" s="9"/>
+      <x:c r="DB39" s="9"/>
+      <x:c r="DC39" s="9"/>
+      <x:c r="DD39" s="9"/>
+      <x:c r="DE39" s="9"/>
+      <x:c r="DF39" s="9"/>
+      <x:c r="DG39" s="9"/>
+      <x:c r="DH39" s="9"/>
+      <x:c r="DI39" s="9"/>
+      <x:c r="DJ39" s="9"/>
+      <x:c r="DK39" s="9"/>
+      <x:c r="DL39" s="9"/>
+      <x:c r="DM39" s="9"/>
+      <x:c r="DN39" s="9"/>
+      <x:c r="DO39" s="9"/>
+      <x:c r="DP39" s="9"/>
+      <x:c r="DQ39" s="9"/>
+      <x:c r="DR39" s="9"/>
+      <x:c r="DS39" s="9"/>
+      <x:c r="DT39" s="9"/>
+      <x:c r="DU39" s="9"/>
+      <x:c r="DV39" s="9"/>
+      <x:c r="DW39" s="9"/>
+      <x:c r="DX39" s="9"/>
+      <x:c r="DY39" s="9"/>
+      <x:c r="DZ39" s="9"/>
+      <x:c r="EA39" s="9"/>
+      <x:c r="EB39" s="9"/>
+      <x:c r="EC39" s="9"/>
+      <x:c r="ED39" s="9"/>
+      <x:c r="EE39" s="9"/>
+      <x:c r="EF39" s="9"/>
+      <x:c r="EG39" s="9"/>
+      <x:c r="EH39" s="9"/>
+      <x:c r="EI39" s="9"/>
+      <x:c r="EJ39" s="9"/>
+      <x:c r="EK39" s="9"/>
+      <x:c r="EL39" s="9"/>
+      <x:c r="EM39" s="9"/>
+      <x:c r="EN39" s="9"/>
+      <x:c r="EO39" s="9"/>
+      <x:c r="EP39" s="9"/>
+      <x:c r="EQ39" s="9"/>
+      <x:c r="ER39" s="9"/>
+      <x:c r="ES39" s="9"/>
+      <x:c r="ET39" s="9"/>
+      <x:c r="EU39" s="9"/>
+      <x:c r="EV39" s="9"/>
+      <x:c r="EW39" s="9"/>
+      <x:c r="EX39" s="9"/>
+      <x:c r="EY39" s="9"/>
+      <x:c r="EZ39" s="9"/>
+      <x:c r="FA39" s="9"/>
+      <x:c r="FB39" s="9"/>
+      <x:c r="FC39" s="9"/>
+      <x:c r="FD39" s="9"/>
+      <x:c r="FE39" s="9"/>
+      <x:c r="FF39" s="9"/>
+      <x:c r="FG39" s="9"/>
+      <x:c r="FH39" s="9"/>
+      <x:c r="FI39" s="9"/>
+      <x:c r="FJ39" s="9"/>
+      <x:c r="FK39" s="9"/>
+      <x:c r="FL39" s="9"/>
+      <x:c r="FM39" s="9"/>
+      <x:c r="FN39" s="9"/>
+      <x:c r="FO39" s="9"/>
+      <x:c r="FP39" s="9"/>
+      <x:c r="FQ39" s="9"/>
+      <x:c r="FR39" s="9"/>
+      <x:c r="FS39" s="20" t="str">
         <x:v>◆</x:v>
       </x:c>
     </x:row>
@@ -7896,7 +8471,7 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="C5" s="25" t="str">
-        <x:v>画面設計書（各画面）</x:v>
+        <x:v>画面設計書（ドラフト済）✅</x:v>
       </x:c>
       <x:c r="D5" s="25" t="str">
         <x:v>れん/ゆうと</x:v>
@@ -7905,10 +8480,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F5" s="25" t="str">
-        <x:v>7/1</x:v>
+        <x:v>6/24</x:v>
       </x:c>
       <x:c r="G5" s="25" t="str">
-        <x:v>7/20</x:v>
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H5" s="25" t="str">
         <x:v>p0c</x:v>
@@ -7922,7 +8497,7 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="C6" s="25" t="str">
-        <x:v>DB設計書（ER・テーブル定義）</x:v>
+        <x:v>DB設計書（ドラフト済）✅</x:v>
       </x:c>
       <x:c r="D6" s="25" t="str">
         <x:v>ひろと</x:v>
@@ -7931,10 +8506,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F6" s="25" t="str">
-        <x:v>7/1</x:v>
+        <x:v>6/24</x:v>
       </x:c>
       <x:c r="G6" s="25" t="str">
-        <x:v>7/15</x:v>
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H6" s="25" t="str">
         <x:v>p0c</x:v>
@@ -7948,7 +8523,7 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="C7" s="25" t="str">
-        <x:v>診断/推薦ロジック仕様</x:v>
+        <x:v>診断/推薦ロジック仕様（ドラフト済）✅</x:v>
       </x:c>
       <x:c r="D7" s="25" t="str">
         <x:v>ひろと/たかと</x:v>
@@ -7957,10 +8532,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F7" s="25" t="str">
-        <x:v>7/8</x:v>
+        <x:v>6/24</x:v>
       </x:c>
       <x:c r="G7" s="25" t="str">
-        <x:v>7/25</x:v>
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H7" s="25" t="str">
         <x:v>p0c</x:v>
@@ -7974,7 +8549,7 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="C8" s="25" t="str">
-        <x:v>薬機法準拠ガイドライン</x:v>
+        <x:v>薬機法準拠ガイドライン（ドラフト済）✅</x:v>
       </x:c>
       <x:c r="D8" s="25" t="str">
         <x:v>たかと</x:v>
@@ -7983,10 +8558,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F8" s="25" t="str">
-        <x:v>7/1</x:v>
+        <x:v>6/24</x:v>
       </x:c>
       <x:c r="G8" s="25" t="str">
-        <x:v>7/18</x:v>
+        <x:v>6/26</x:v>
       </x:c>
       <x:c r="H8" s="25" t="str">
         <x:v>p0c</x:v>
@@ -8009,10 +8584,10 @@
         <x:v>基盤</x:v>
       </x:c>
       <x:c r="F9" s="25" t="str">
+        <x:v>7/1</x:v>
+      </x:c>
+      <x:c r="G9" s="25" t="str">
         <x:v>7/10</x:v>
-      </x:c>
-      <x:c r="G9" s="25" t="str">
-        <x:v>7/25</x:v>
       </x:c>
       <x:c r="H9" s="25" t="str">
         <x:v>p1b,p1c,p1d</x:v>
@@ -8090,7 +8665,7 @@
         <x:v>6/26</x:v>
       </x:c>
       <x:c r="G12" s="25" t="str">
-        <x:v>7/15</x:v>
+        <x:v>7/6</x:v>
       </x:c>
       <x:c r="H12" s="25" t="str">
         <x:v>p2a</x:v>
@@ -8116,7 +8691,7 @@
         <x:v>7/1</x:v>
       </x:c>
       <x:c r="G13" s="25" t="str">
-        <x:v>7/18</x:v>
+        <x:v>7/10</x:v>
       </x:c>
       <x:c r="H13" s="25" t="str">
         <x:v>p2a</x:v>
@@ -8124,16 +8699,16 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="25" t="str">
-        <x:v>p2b</x:v>
+        <x:v>p2e</x:v>
       </x:c>
       <x:c r="B14" s="25" t="str">
         <x:v>P2</x:v>
       </x:c>
       <x:c r="C14" s="25" t="str">
-        <x:v>Supabase初期構築・RLS</x:v>
+        <x:v>ダミーデータ・型定義・基盤完成→developマージ</x:v>
       </x:c>
       <x:c r="D14" s="25" t="str">
-        <x:v>村上/ひろと</x:v>
+        <x:v>村上</x:v>
       </x:c>
       <x:c r="E14" s="25" t="str">
         <x:v>基盤</x:v>
@@ -8142,21 +8717,21 @@
         <x:v>7/8</x:v>
       </x:c>
       <x:c r="G14" s="25" t="str">
-        <x:v>7/22</x:v>
+        <x:v>7/15</x:v>
       </x:c>
       <x:c r="H14" s="25" t="str">
-        <x:v>p2a,p1c</x:v>
+        <x:v>p2c,p2d,p1g</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="25" t="str">
-        <x:v>p2e</x:v>
+        <x:v>mbase</x:v>
       </x:c>
       <x:c r="B15" s="25" t="str">
-        <x:v>P2</x:v>
+        <x:v>M</x:v>
       </x:c>
       <x:c r="C15" s="25" t="str">
-        <x:v>ダミーデータ・型定義・基盤完成→developマージ</x:v>
+        <x:v>★ M-Base 基盤アプリ完成（developマージ）</x:v>
       </x:c>
       <x:c r="D15" s="25" t="str">
         <x:v>村上</x:v>
@@ -8168,10 +8743,10 @@
         <x:v>7/15</x:v>
       </x:c>
       <x:c r="G15" s="25" t="str">
-        <x:v>7/31</x:v>
+        <x:v>7/15</x:v>
       </x:c>
       <x:c r="H15" s="25" t="str">
-        <x:v>p2c,p2d,p2b,p1g</x:v>
+        <x:v>p2e</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8182,7 +8757,7 @@
         <x:v>P3</x:v>
       </x:c>
       <x:c r="C16" s="25" t="str">
-        <x:v>商品マスター30-50整備</x:v>
+        <x:v>商品マスター 最小整備(15-20)</x:v>
       </x:c>
       <x:c r="D16" s="25" t="str">
         <x:v>たかと</x:v>
@@ -8191,10 +8766,10 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F16" s="25" t="str">
-        <x:v>8/1</x:v>
+        <x:v>7/10</x:v>
       </x:c>
       <x:c r="G16" s="25" t="str">
-        <x:v>8/31</x:v>
+        <x:v>8/5</x:v>
       </x:c>
       <x:c r="H16" s="25" t="str">
         <x:v>p1c,p1f</x:v>
@@ -8202,54 +8777,54 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="25" t="str">
-        <x:v>p3b</x:v>
+        <x:v>p3c</x:v>
       </x:c>
       <x:c r="B17" s="25" t="str">
         <x:v>P3</x:v>
       </x:c>
       <x:c r="C17" s="25" t="str">
-        <x:v>成分タグ・事実情報整備</x:v>
+        <x:v>ロードマップ概念データ</x:v>
       </x:c>
       <x:c r="D17" s="25" t="str">
-        <x:v>たかと</x:v>
+        <x:v>たかと/ひろと</x:v>
       </x:c>
       <x:c r="E17" s="25" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="F17" s="25" t="str">
-        <x:v>8/15</x:v>
+        <x:v>7/12</x:v>
       </x:c>
       <x:c r="G17" s="25" t="str">
-        <x:v>9/5</x:v>
+        <x:v>8/2</x:v>
       </x:c>
       <x:c r="H17" s="25" t="str">
-        <x:v>p3a,p1f</x:v>
+        <x:v>p1d</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="25" t="str">
-        <x:v>p3c</x:v>
+        <x:v>p3b</x:v>
       </x:c>
       <x:c r="B18" s="25" t="str">
         <x:v>P3</x:v>
       </x:c>
       <x:c r="C18" s="25" t="str">
-        <x:v>ロードマップ概念データ</x:v>
+        <x:v>成分タグ・事実情報整備</x:v>
       </x:c>
       <x:c r="D18" s="25" t="str">
-        <x:v>たかと/ひろと</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E18" s="25" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="F18" s="25" t="str">
-        <x:v>8/20</x:v>
+        <x:v>7/20</x:v>
       </x:c>
       <x:c r="G18" s="25" t="str">
-        <x:v>9/10</x:v>
+        <x:v>8/10</x:v>
       </x:c>
       <x:c r="H18" s="25" t="str">
-        <x:v>p1d</x:v>
+        <x:v>p3a,p1f</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8269,10 +8844,10 @@
         <x:v>feature/diagnosis-logic</x:v>
       </x:c>
       <x:c r="F19" s="25" t="str">
-        <x:v>8/1</x:v>
+        <x:v>7/16</x:v>
       </x:c>
       <x:c r="G19" s="25" t="str">
-        <x:v>8/31</x:v>
+        <x:v>8/5</x:v>
       </x:c>
       <x:c r="H19" s="25" t="str">
         <x:v>p2e,p1d</x:v>
@@ -8295,10 +8870,10 @@
         <x:v>feature/sc01-check-ui</x:v>
       </x:c>
       <x:c r="F20" s="25" t="str">
-        <x:v>8/1</x:v>
+        <x:v>7/16</x:v>
       </x:c>
       <x:c r="G20" s="25" t="str">
-        <x:v>8/31</x:v>
+        <x:v>8/8</x:v>
       </x:c>
       <x:c r="H20" s="25" t="str">
         <x:v>p2e,p1b</x:v>
@@ -8321,10 +8896,10 @@
         <x:v>feature/roadmap-logic</x:v>
       </x:c>
       <x:c r="F21" s="25" t="str">
-        <x:v>8/20</x:v>
+        <x:v>7/28</x:v>
       </x:c>
       <x:c r="G21" s="25" t="str">
-        <x:v>9/15</x:v>
+        <x:v>8/12</x:v>
       </x:c>
       <x:c r="H21" s="25" t="str">
         <x:v>p4b,p3c</x:v>
@@ -8332,132 +8907,132 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="25" t="str">
-        <x:v>p4c</x:v>
+        <x:v>p4f</x:v>
       </x:c>
       <x:c r="B22" s="25" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="C22" s="25" t="str">
-        <x:v>SC-02 ロードマップUI</x:v>
+        <x:v>ディスクレーマー共通部品</x:v>
       </x:c>
       <x:c r="D22" s="25" t="str">
-        <x:v>れん</x:v>
+        <x:v>村上</x:v>
       </x:c>
       <x:c r="E22" s="25" t="str">
-        <x:v>feature/sc02-roadmap-ui</x:v>
+        <x:v>基盤/feature</x:v>
       </x:c>
       <x:c r="F22" s="25" t="str">
-        <x:v>9/1</x:v>
+        <x:v>7/28</x:v>
       </x:c>
       <x:c r="G22" s="25" t="str">
-        <x:v>9/25</x:v>
+        <x:v>8/8</x:v>
       </x:c>
       <x:c r="H22" s="25" t="str">
-        <x:v>p4g,p2e</x:v>
+        <x:v>p1f</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="25" t="str">
-        <x:v>p4h</x:v>
+        <x:v>p4c</x:v>
       </x:c>
       <x:c r="B23" s="25" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="C23" s="25" t="str">
-        <x:v>推薦ロジック（純粋関数）</x:v>
+        <x:v>SC-02 ロードマップUI</x:v>
       </x:c>
       <x:c r="D23" s="25" t="str">
-        <x:v>たかと</x:v>
+        <x:v>れん</x:v>
       </x:c>
       <x:c r="E23" s="25" t="str">
-        <x:v>feature/recommend-logic</x:v>
+        <x:v>feature/sc02-roadmap-ui</x:v>
       </x:c>
       <x:c r="F23" s="25" t="str">
-        <x:v>9/1</x:v>
+        <x:v>8/1</x:v>
       </x:c>
       <x:c r="G23" s="25" t="str">
-        <x:v>9/25</x:v>
+        <x:v>8/18</x:v>
       </x:c>
       <x:c r="H23" s="25" t="str">
-        <x:v>p3b,p1d</x:v>
+        <x:v>p4g,p2e</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="25" t="str">
-        <x:v>p4d</x:v>
+        <x:v>p4h</x:v>
       </x:c>
       <x:c r="B24" s="25" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="C24" s="25" t="str">
-        <x:v>SC-03 商品比較UI</x:v>
+        <x:v>推薦ロジック（最小・純粋関数）</x:v>
       </x:c>
       <x:c r="D24" s="25" t="str">
-        <x:v>ゆうと</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E24" s="25" t="str">
-        <x:v>feature/sc03-product-compare-ui</x:v>
+        <x:v>feature/recommend-logic</x:v>
       </x:c>
       <x:c r="F24" s="25" t="str">
-        <x:v>9/15</x:v>
+        <x:v>8/1</x:v>
       </x:c>
       <x:c r="G24" s="25" t="str">
-        <x:v>10/10</x:v>
+        <x:v>8/15</x:v>
       </x:c>
       <x:c r="H24" s="25" t="str">
-        <x:v>p4h,p3b,p2e</x:v>
+        <x:v>p3a,p1d</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="25" t="str">
-        <x:v>p4e</x:v>
+        <x:v>p4d</x:v>
       </x:c>
       <x:c r="B25" s="25" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="C25" s="25" t="str">
-        <x:v>SC-04 継続記録UI</x:v>
+        <x:v>SC-03 商品比較UI</x:v>
       </x:c>
       <x:c r="D25" s="25" t="str">
         <x:v>ゆうと</x:v>
       </x:c>
       <x:c r="E25" s="25" t="str">
-        <x:v>feature/sc04-record-ui</x:v>
+        <x:v>feature/sc03-product-compare-ui</x:v>
       </x:c>
       <x:c r="F25" s="25" t="str">
-        <x:v>10/1</x:v>
+        <x:v>8/8</x:v>
       </x:c>
       <x:c r="G25" s="25" t="str">
-        <x:v>10/15</x:v>
+        <x:v>8/22</x:v>
       </x:c>
       <x:c r="H25" s="25" t="str">
-        <x:v>p2e</x:v>
+        <x:v>p4h,p3a,p2e</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="25" t="str">
-        <x:v>p4f</x:v>
+        <x:v>p4e</x:v>
       </x:c>
       <x:c r="B26" s="25" t="str">
         <x:v>P4</x:v>
       </x:c>
       <x:c r="C26" s="25" t="str">
-        <x:v>ディスクレーマー共通部品</x:v>
+        <x:v>SC-04 継続記録UI</x:v>
       </x:c>
       <x:c r="D26" s="25" t="str">
-        <x:v>村上</x:v>
+        <x:v>ゆうと</x:v>
       </x:c>
       <x:c r="E26" s="25" t="str">
-        <x:v>基盤/feature</x:v>
+        <x:v>feature/sc04-record-ui</x:v>
       </x:c>
       <x:c r="F26" s="25" t="str">
-        <x:v>8/20</x:v>
+        <x:v>8/12</x:v>
       </x:c>
       <x:c r="G26" s="25" t="str">
-        <x:v>9/5</x:v>
+        <x:v>8/25</x:v>
       </x:c>
       <x:c r="H26" s="25" t="str">
-        <x:v>p1f</x:v>
+        <x:v>p2e</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -8468,7 +9043,7 @@
         <x:v>P5</x:v>
       </x:c>
       <x:c r="C27" s="25" t="str">
-        <x:v>develop 統合・通しデモ</x:v>
+        <x:v>develop統合・通しデモ（最小MVP）</x:v>
       </x:c>
       <x:c r="D27" s="25" t="str">
         <x:v>全員</x:v>
@@ -8477,36 +9052,36 @@
         <x:v>develop</x:v>
       </x:c>
       <x:c r="F27" s="25" t="str">
-        <x:v>10/16</x:v>
+        <x:v>8/22</x:v>
       </x:c>
       <x:c r="G27" s="25" t="str">
-        <x:v>10/22</x:v>
+        <x:v>8/27</x:v>
       </x:c>
       <x:c r="H27" s="25" t="str">
-        <x:v>p4a-p4h</x:v>
+        <x:v>p4a,p4b,p4c,p4d,p4e</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="25" t="str">
-        <x:v>p5b</x:v>
+        <x:v>p5c</x:v>
       </x:c>
       <x:c r="B28" s="25" t="str">
         <x:v>P5</x:v>
       </x:c>
       <x:c r="C28" s="25" t="str">
-        <x:v>機能/アクセシビリティテスト</x:v>
+        <x:v>薬機法表現チェック（公開前）</x:v>
       </x:c>
       <x:c r="D28" s="25" t="str">
-        <x:v>村上/全員</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E28" s="25" t="str">
         <x:v>develop</x:v>
       </x:c>
       <x:c r="F28" s="25" t="str">
-        <x:v>10/20</x:v>
+        <x:v>8/24</x:v>
       </x:c>
       <x:c r="G28" s="25" t="str">
-        <x:v>10/28</x:v>
+        <x:v>8/29</x:v>
       </x:c>
       <x:c r="H28" s="25" t="str">
         <x:v>p5a</x:v>
@@ -8514,39 +9089,39 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="25" t="str">
-        <x:v>p5c</x:v>
+        <x:v>p5d</x:v>
       </x:c>
       <x:c r="B29" s="25" t="str">
         <x:v>P5</x:v>
       </x:c>
       <x:c r="C29" s="25" t="str">
-        <x:v>薬機法表現チェック</x:v>
+        <x:v>最小MVP Web公開（GitHub Pages）</x:v>
       </x:c>
       <x:c r="D29" s="25" t="str">
-        <x:v>たかと</x:v>
+        <x:v>村上</x:v>
       </x:c>
       <x:c r="E29" s="25" t="str">
         <x:v>develop</x:v>
       </x:c>
       <x:c r="F29" s="25" t="str">
-        <x:v>10/22</x:v>
+        <x:v>8/27</x:v>
       </x:c>
       <x:c r="G29" s="25" t="str">
-        <x:v>10/31</x:v>
+        <x:v>8/31</x:v>
       </x:c>
       <x:c r="H29" s="25" t="str">
-        <x:v>p5a</x:v>
+        <x:v>p5a,p5c</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25" t="str">
-        <x:v>p6a</x:v>
+        <x:v>m_mvp</x:v>
       </x:c>
       <x:c r="B30" s="25" t="str">
-        <x:v>P6</x:v>
+        <x:v>M</x:v>
       </x:c>
       <x:c r="C30" s="25" t="str">
-        <x:v>デモシナリオ・発表資料</x:v>
+        <x:v>★ M-MVP 最小アプリ Web公開（8月末・WEB動作）</x:v>
       </x:c>
       <x:c r="D30" s="25" t="str">
         <x:v>全員</x:v>
@@ -8555,90 +9130,168 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="F30" s="25" t="str">
-        <x:v>11/1</x:v>
+        <x:v>8/31</x:v>
       </x:c>
       <x:c r="G30" s="25" t="str">
-        <x:v>11/10</x:v>
+        <x:v>8/31</x:v>
       </x:c>
       <x:c r="H30" s="25" t="str">
-        <x:v>p5b,p5c</x:v>
+        <x:v>p5d</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="25" t="str">
-        <x:v>p6b</x:v>
+        <x:v>p2b</x:v>
       </x:c>
       <x:c r="B31" s="25" t="str">
-        <x:v>P6</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="C31" s="25" t="str">
-        <x:v>リハーサル・最終調整</x:v>
+        <x:v>Supabase連携（最小MVP後・拡張）</x:v>
       </x:c>
       <x:c r="D31" s="25" t="str">
-        <x:v>全員</x:v>
+        <x:v>村上/ひろと</x:v>
       </x:c>
       <x:c r="E31" s="25" t="str">
-        <x:v>—</x:v>
+        <x:v>基盤</x:v>
       </x:c>
       <x:c r="F31" s="25" t="str">
-        <x:v>11/8</x:v>
+        <x:v>9/1</x:v>
       </x:c>
       <x:c r="G31" s="25" t="str">
-        <x:v>11/15</x:v>
+        <x:v>9/15</x:v>
       </x:c>
       <x:c r="H31" s="25" t="str">
-        <x:v>p6a</x:v>
+        <x:v>p2e</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="25" t="str">
-        <x:v>mbase</x:v>
+        <x:v>p3d</x:v>
       </x:c>
       <x:c r="B32" s="25" t="str">
-        <x:v>M</x:v>
+        <x:v>P3</x:v>
       </x:c>
       <x:c r="C32" s="25" t="str">
-        <x:v>★ M-Base 基盤アプリ完成（developマージ）</x:v>
+        <x:v>商品マスター拡充(30-50)</x:v>
       </x:c>
       <x:c r="D32" s="25" t="str">
-        <x:v>村上</x:v>
+        <x:v>たかと</x:v>
       </x:c>
       <x:c r="E32" s="25" t="str">
-        <x:v>基盤</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="F32" s="25" t="str">
-        <x:v>7/31</x:v>
+        <x:v>9/1</x:v>
       </x:c>
       <x:c r="G32" s="25" t="str">
-        <x:v>7/31</x:v>
+        <x:v>9/25</x:v>
       </x:c>
       <x:c r="H32" s="25" t="str">
-        <x:v>p2e</x:v>
+        <x:v>p3a</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="25" t="str">
+        <x:v>p5b</x:v>
+      </x:c>
+      <x:c r="B33" s="25" t="str">
+        <x:v>P5</x:v>
+      </x:c>
+      <x:c r="C33" s="25" t="str">
+        <x:v>機能/アクセシビリティテスト</x:v>
+      </x:c>
+      <x:c r="D33" s="25" t="str">
+        <x:v>村上/全員</x:v>
+      </x:c>
+      <x:c r="E33" s="25" t="str">
+        <x:v>develop</x:v>
+      </x:c>
+      <x:c r="F33" s="25" t="str">
+        <x:v>10/1</x:v>
+      </x:c>
+      <x:c r="G33" s="25" t="str">
+        <x:v>10/22</x:v>
+      </x:c>
+      <x:c r="H33" s="25" t="str">
+        <x:v>p5d,p3d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="25" t="str">
+        <x:v>p6a</x:v>
+      </x:c>
+      <x:c r="B34" s="25" t="str">
+        <x:v>P6</x:v>
+      </x:c>
+      <x:c r="C34" s="25" t="str">
+        <x:v>デモシナリオ・発表資料</x:v>
+      </x:c>
+      <x:c r="D34" s="25" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="E34" s="25" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F34" s="25" t="str">
+        <x:v>11/1</x:v>
+      </x:c>
+      <x:c r="G34" s="25" t="str">
+        <x:v>11/10</x:v>
+      </x:c>
+      <x:c r="H34" s="25" t="str">
+        <x:v>p5b</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="25" t="str">
+        <x:v>p6b</x:v>
+      </x:c>
+      <x:c r="B35" s="25" t="str">
+        <x:v>P6</x:v>
+      </x:c>
+      <x:c r="C35" s="25" t="str">
+        <x:v>リハーサル・最終調整</x:v>
+      </x:c>
+      <x:c r="D35" s="25" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="E35" s="25" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F35" s="25" t="str">
+        <x:v>11/8</x:v>
+      </x:c>
+      <x:c r="G35" s="25" t="str">
+        <x:v>11/15</x:v>
+      </x:c>
+      <x:c r="H35" s="25" t="str">
+        <x:v>p6a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="25" t="str">
         <x:v>m1</x:v>
       </x:c>
-      <x:c r="B33" s="25" t="str">
+      <x:c r="B36" s="25" t="str">
         <x:v>M</x:v>
       </x:c>
-      <x:c r="C33" s="25" t="str">
+      <x:c r="C36" s="25" t="str">
         <x:v>★ 中間発表（マイルストーン）</x:v>
       </x:c>
-      <x:c r="D33" s="25" t="str">
+      <x:c r="D36" s="25" t="str">
         <x:v>全員</x:v>
       </x:c>
-      <x:c r="E33" s="25" t="str">
+      <x:c r="E36" s="25" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="F33" s="25" t="str">
+      <x:c r="F36" s="25" t="str">
         <x:v>11/15</x:v>
       </x:c>
-      <x:c r="G33" s="25" t="str">
+      <x:c r="G36" s="25" t="str">
         <x:v>11/15</x:v>
       </x:c>
-      <x:c r="H33" s="25" t="str">
+      <x:c r="H36" s="25" t="str">
         <x:v>p6b</x:v>
       </x:c>
     </x:row>
@@ -8658,14 +9311,14 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="28" t="str">
-        <x:v>進め方（v2.0）</x:v>
+        <x:v>進め方（v2.1）</x:v>
       </x:c>
       <x:c r="B1" s="28"/>
       <x:c r="C1" s="28"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="25" t="str">
-        <x:v>まず村上が基盤アプリを先行構築し、7/31 に develop へマージ（M-Base）。設定ボタンは feature/settings-button で完了済みとして P2 に反映。以降、各機能を命名制約に沿った feature ブランチで分担して追加する。</x:v>
+        <x:v>主目標を『2026/08/31 に最小機能アプリをWeb公開（M-MVP）』に設定。まず村上が基盤アプリを先行構築し 7/15 に develop へマージ（M-Base）。以降、各機能を feature ブランチで分担し、最小スコープ（4画面・ローカルデータ・GitHub Pages公開）を8月末に達成する。Supabase連携・商品データ拡充(30-50)・本格テストは9〜10月、中間発表は11月。</x:v>
       </x:c>
       <x:c r="B2" s="25"/>
       <x:c r="C2" s="25"/>
@@ -8701,7 +9354,7 @@
         <x:v>リーダー・品質管理者</x:v>
       </x:c>
       <x:c r="C6" s="25" t="str">
-        <x:v>基盤アプリ構築・feature/settings-button・共有部品・デザイントークン・進捗管理・マージ/レビュー</x:v>
+        <x:v>基盤アプリ構築・共有部品・デザイントークン・Web公開・進捗管理・マージ/レビュー</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -8784,13 +9437,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="25" t="str">
-        <x:v>P1 詳細設計</x:v>
+        <x:v>P1 詳細設計（ドラフト済→確定）</x:v>
       </x:c>
       <x:c r="B15" s="25" t="str">
-        <x:v>2026-07-01〜2026-07-31</x:v>
+        <x:v>2026-06-24〜2026-07-10</x:v>
       </x:c>
       <x:c r="C15" s="25" t="str">
-        <x:v>画面設計書・DB設計書・診断/推薦ロジック仕様・薬機法ガイドライン・機能IF（型）定義</x:v>
+        <x:v>画面/DB/診断・推薦/薬機法の各設計（ドラフト済）・機能IF（型）定義</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8798,43 +9451,43 @@
         <x:v>P2 基盤アプリ構築（村上・先行）</x:v>
       </x:c>
       <x:c r="B16" s="25" t="str">
-        <x:v>2026-06-19〜2026-07-31</x:v>
+        <x:v>2026-06-19〜2026-07-15</x:v>
       </x:c>
       <x:c r="C16" s="25" t="str">
-        <x:v>リポジトリ・PWA雛形・設定ボタン・Supabase初期・デザイントークン・共有部品・ルーティング・4画面の空ハコ・ダミーデータ・型定義</x:v>
+        <x:v>リポジトリ・PWA雛形・設定ボタン・デザイントークン・共有部品・ルーティング・4画面の空ハコ・ダミーデータ・型定義（M-Base 7/15）／Supabase連携は最小MVP後</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="25" t="str">
-        <x:v>P3 データ整備</x:v>
+        <x:v>P3 データ整備（最小→拡充）</x:v>
       </x:c>
       <x:c r="B17" s="25" t="str">
-        <x:v>2026-08-01〜2026-09-10</x:v>
+        <x:v>2026-07-10〜2026-09-25</x:v>
       </x:c>
       <x:c r="C17" s="25" t="str">
-        <x:v>商品マスター30-50・成分タグ・ロードマップ概念データ</x:v>
+        <x:v>商品マスター最小(15-20)→拡充(30-50)・成分タグ・ロードマップ概念データ</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="25" t="str">
-        <x:v>P4 機能実装（feature 分担）</x:v>
+        <x:v>P4 機能実装（最小・feature分担）</x:v>
       </x:c>
       <x:c r="B18" s="25" t="str">
-        <x:v>2026-08-01〜2026-10-15</x:v>
+        <x:v>2026-07-16〜2026-08-25</x:v>
       </x:c>
       <x:c r="C18" s="25" t="str">
-        <x:v>各 feature ブランチで SC-01〜04・診断/ロードマップ/推薦ロジック・ディスクレーマー</x:v>
+        <x:v>各 feature で SC-01〜04・診断/ロードマップ/推薦(最小)・ディスクレーマー</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="25" t="str">
-        <x:v>P5 結合・テスト</x:v>
+        <x:v>P5 結合・Web公開／テスト</x:v>
       </x:c>
       <x:c r="B19" s="25" t="str">
-        <x:v>2026-10-16〜2026-10-31</x:v>
+        <x:v>2026-08-22〜2026-10-22</x:v>
       </x:c>
       <x:c r="C19" s="25" t="str">
-        <x:v>develop 統合・通しデモ・機能/アクセシビリティテスト・薬機法表現チェック</x:v>
+        <x:v>develop統合・通しデモ・薬機法チェック・GitHub Pages公開（8/31）・機能/アクセシビリティテスト</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -8850,36 +9503,58 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="25" t="str">
+        <x:v>★ M-MVP 最小アプリ Web公開</x:v>
+      </x:c>
+      <x:c r="B21" s="25" t="str">
+        <x:v>2026-08-31</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="str">
+        <x:v>4画面がWeb上で動作（ローカルデータ）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="25" t="str">
         <x:v>★ 中間発表</x:v>
       </x:c>
-      <x:c r="B21" s="25" t="str">
+      <x:c r="B22" s="25" t="str">
         <x:v>2026-11</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="str">
-        <x:v>MVP動作デモ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="25"/>
-      <x:c r="B22" s="25"/>
-      <x:c r="C22" s="25"/>
+      <x:c r="C22" s="25" t="str">
+        <x:v>拡張版MVP動作デモ</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="29" t="str">
+      <x:c r="A23" s="25"/>
+      <x:c r="B23" s="25"/>
+      <x:c r="C23" s="25"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="29" t="str">
         <x:v>更新メモ</x:v>
       </x:c>
-      <x:c r="B23" s="29"/>
-      <x:c r="C23" s="29"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="25" t="str">
+      <x:c r="B24" s="29"/>
+      <x:c r="C24" s="29"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="25" t="str">
         <x:v>2026-06-19</x:v>
       </x:c>
-      <x:c r="B24" s="25" t="str">
+      <x:c r="B25" s="25" t="str">
         <x:v>v2.0追記</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="str">
-        <x:v>feature/settings-button の完了を P2 タスクへ追加。feature ブランチ名を ASCII/kebab-case に統一。ガント横軸を週単位から日単位（1日1列）へ変更。</x:v>
+      <x:c r="C25" s="25" t="str">
+        <x:v>feature/settings-button の完了を P2 へ追加。feature ブランチ名を ASCII/kebab-case に統一。ガント横軸を日単位（1日1列）へ変更。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="25" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="B26" s="25" t="str">
+        <x:v>v2.1</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="str">
+        <x:v>主目標を『8月末 最小アプリWeb公開（M-MVP）』に設定。基盤を前倒し（M-Base 7/15）、P3最小データ・P4最小機能を7〜8月に圧縮、最小MVP Web公開(p5d)を追加。Supabase連携・データ拡充(30-50)・本格テストは9〜10月へ。設計書13本のドラフト前倒し完了を反映。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8887,7 +9562,7 @@
     <x:mergeCell ref="A1:C1"/>
     <x:mergeCell ref="A4:C4"/>
     <x:mergeCell ref="A12:C12"/>
-    <x:mergeCell ref="A23:C23"/>
+    <x:mergeCell ref="A24:C24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
